--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBF624B-699B-44CA-AB5A-BBABEC1725D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652DA3B1-B6DF-4CE4-A3A8-DA7E1F4025A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
+    <workbookView xWindow="-28920" yWindow="450" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="85">
   <si>
     <t>Colonne A</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Roll-Up Pro - Bâche  Polyester 420 Gr certifié M1 (résistance au feu) occultant Impression Quadri - REcto</t>
   </si>
   <si>
-    <t>Flyer A6</t>
-  </si>
-  <si>
     <t>135g couché brillant</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>115g recyclé</t>
-  </si>
-  <si>
-    <t>Flyer A5</t>
   </si>
   <si>
     <t>Dépliant</t>
@@ -270,7 +264,37 @@
     <t>Roll-Up Pro</t>
   </si>
   <si>
-    <t>350g couché demi mat</t>
+    <t>A6 - 115g recyclé</t>
+  </si>
+  <si>
+    <t>A6 - 350g couché demi mat</t>
+  </si>
+  <si>
+    <t>A6 - 250g couché brillant ou demi mat</t>
+  </si>
+  <si>
+    <t>A6 - 170g couché demi mat</t>
+  </si>
+  <si>
+    <t>A6 - 135g couché brillant</t>
+  </si>
+  <si>
+    <t>Flyer</t>
+  </si>
+  <si>
+    <t>A5 - 135g couché brillant</t>
+  </si>
+  <si>
+    <t>A5 - 170g couché demi mat</t>
+  </si>
+  <si>
+    <t>A5 - 250g couché brillant ou demi mat</t>
+  </si>
+  <si>
+    <t>A5 - 350g couché demi mat</t>
+  </si>
+  <si>
+    <t>A5 - 115g recyclé</t>
   </si>
 </sst>
 </file>
@@ -787,7 +811,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -831,13 +855,13 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
       </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3">
@@ -864,13 +888,13 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
@@ -897,13 +921,13 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5">
@@ -930,13 +954,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6">
@@ -963,13 +987,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7">
@@ -996,13 +1020,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8">
@@ -1032,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -1057,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1082,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -1107,7 +1131,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -1129,13 +1153,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1167,13 +1191,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1204,13 +1228,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1241,13 +1265,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1278,13 +1302,13 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1315,13 +1339,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1352,13 +1376,13 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1389,13 +1413,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1426,13 +1450,13 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1463,13 +1487,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1500,13 +1524,13 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
         <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>17</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1537,13 +1561,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1574,13 +1598,13 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1611,13 +1635,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1648,13 +1672,13 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1685,13 +1709,13 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1722,13 +1746,13 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1759,13 +1783,13 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1796,13 +1820,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1833,13 +1857,13 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1870,13 +1894,13 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
         <v>23</v>
       </c>
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1907,13 +1931,13 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
         <v>23</v>
       </c>
-      <c r="B34" t="s">
-        <v>25</v>
-      </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1944,13 +1968,13 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
         <v>23</v>
       </c>
-      <c r="B35" t="s">
-        <v>25</v>
-      </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1981,13 +2005,13 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" t="s">
-        <v>25</v>
-      </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2018,13 +2042,13 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2055,13 +2079,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2092,13 +2116,13 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2129,13 +2153,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2166,13 +2190,13 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2203,13 +2227,13 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2240,13 +2264,13 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2277,13 +2301,13 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2314,13 +2338,13 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2351,13 +2375,13 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2388,13 +2412,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2425,13 +2449,13 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2460,13 +2484,13 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2495,13 +2519,13 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" t="s">
         <v>29</v>
       </c>
-      <c r="B50" t="s">
-        <v>31</v>
-      </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2530,13 +2554,13 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2573,13 +2597,13 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" t="s">
         <v>32</v>
       </c>
-      <c r="B52" t="s">
-        <v>34</v>
-      </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2616,13 +2640,13 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2659,13 +2683,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D54">
         <v>31.680000000000003</v>
@@ -2702,13 +2726,13 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>34</v>
+      </c>
+      <c r="B55" t="s">
         <v>36</v>
       </c>
-      <c r="B55" t="s">
-        <v>38</v>
-      </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D55">
         <v>61.600000000000009</v>
@@ -2745,13 +2769,13 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D56">
         <v>46.2</v>
@@ -2784,13 +2808,13 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D57">
         <v>31.680000000000003</v>
@@ -2827,13 +2851,13 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D58">
         <v>70.400000000000006</v>
@@ -2868,13 +2892,13 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D59">
         <v>129.03</v>
@@ -2907,13 +2931,13 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2938,13 +2962,13 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2969,13 +2993,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" t="s">
         <v>41</v>
       </c>
-      <c r="B62" t="s">
-        <v>43</v>
-      </c>
       <c r="C62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3000,13 +3024,13 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" t="s">
         <v>41</v>
       </c>
-      <c r="B63" t="s">
-        <v>43</v>
-      </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3031,13 +3055,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" t="s">
         <v>44</v>
       </c>
-      <c r="B64" t="s">
-        <v>46</v>
-      </c>
       <c r="C64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3066,13 +3090,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C65" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3101,13 +3125,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C66" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3136,13 +3160,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" t="s">
         <v>44</v>
       </c>
-      <c r="B67" t="s">
-        <v>46</v>
-      </c>
       <c r="C67" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3177,13 +3201,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" t="s">
         <v>47</v>
-      </c>
-      <c r="C68" t="s">
-        <v>49</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3218,13 +3242,13 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -3249,13 +3273,13 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D70">
         <v>75.375</v>
@@ -3274,13 +3298,13 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D71">
         <v>87.5</v>
@@ -3299,13 +3323,13 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B72" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D72">
         <v>124.25</v>
@@ -3324,13 +3348,13 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73">
         <v>150.5</v>
@@ -3349,13 +3373,13 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D74">
         <v>176.75</v>
@@ -3374,13 +3398,13 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3409,13 +3433,13 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" t="s">
         <v>57</v>
       </c>
-      <c r="B76" t="s">
-        <v>59</v>
-      </c>
       <c r="C76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3444,13 +3468,13 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B77" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3479,13 +3503,13 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B78" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -3514,13 +3538,13 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -3547,13 +3571,13 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>60</v>
+      </c>
+      <c r="B80" t="s">
         <v>62</v>
       </c>
-      <c r="B80" t="s">
-        <v>64</v>
-      </c>
       <c r="C80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -3580,13 +3604,13 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B81" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -3613,13 +3637,13 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B82" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3646,13 +3670,13 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B83" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3679,13 +3703,13 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652DA3B1-B6DF-4CE4-A3A8-DA7E1F4025A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50112438-2F2E-4E48-88C3-A79E42A3F41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="450" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -159,9 +159,6 @@
 chrome brillant 80g</t>
   </si>
   <si>
-    <t>CARTE DE VISITE - FORMAT STANDARD</t>
-  </si>
-  <si>
     <t>sans pelliculage</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>A5 - 115g recyclé</t>
+  </si>
+  <si>
+    <t>CARTE DE VISITE</t>
   </si>
 </sst>
 </file>
@@ -855,10 +855,10 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -888,13 +888,13 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
         <v>67</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
@@ -921,10 +921,10 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -954,13 +954,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" t="s">
         <v>67</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6">
@@ -987,10 +987,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
         <v>67</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8">
@@ -1056,7 +1056,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1106,7 +1106,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -1131,7 +1131,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -1153,10 +1153,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1191,13 +1191,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -1265,13 +1265,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -1339,13 +1339,13 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -1413,13 +1413,13 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1450,10 +1450,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -1487,13 +1487,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1524,10 +1524,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -1561,13 +1561,13 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
         <v>79</v>
       </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
       <c r="C24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -1635,13 +1635,13 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1672,10 +1672,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -1709,13 +1709,13 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -1783,13 +1783,13 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2455,7 +2455,7 @@
         <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2490,7 +2490,7 @@
         <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2525,7 +2525,7 @@
         <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
         <v>39</v>
-      </c>
-      <c r="B60" t="s">
-        <v>40</v>
       </c>
       <c r="C60" t="s">
         <v>16</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" t="s">
         <v>39</v>
-      </c>
-      <c r="B61" t="s">
-        <v>40</v>
       </c>
       <c r="C61" t="s">
         <v>17</v>
@@ -2993,10 +2993,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
         <v>16</v>
@@ -3024,10 +3024,10 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C63" t="s">
         <v>17</v>
@@ -3055,13 +3055,13 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
         <v>42</v>
-      </c>
-      <c r="B64" t="s">
-        <v>44</v>
-      </c>
-      <c r="C64" t="s">
-        <v>43</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3090,13 +3090,13 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" t="s">
         <v>42</v>
-      </c>
-      <c r="B65" t="s">
-        <v>45</v>
-      </c>
-      <c r="C65" t="s">
-        <v>43</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3125,13 +3125,13 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" t="s">
         <v>42</v>
-      </c>
-      <c r="B66" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" t="s">
-        <v>43</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3160,13 +3160,13 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
         <v>16</v>
@@ -3273,10 +3273,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C70" t="s">
         <v>16</v>
@@ -3298,10 +3298,10 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C71" t="s">
         <v>16</v>
@@ -3323,10 +3323,10 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C72" t="s">
         <v>16</v>
@@ -3348,10 +3348,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C73" t="s">
         <v>16</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C74" t="s">
         <v>16</v>
@@ -3398,10 +3398,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" t="s">
         <v>55</v>
-      </c>
-      <c r="B75" t="s">
-        <v>56</v>
       </c>
       <c r="C75" t="s">
         <v>16</v>
@@ -3433,10 +3433,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C76" t="s">
         <v>17</v>
@@ -3468,10 +3468,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -3503,10 +3503,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C78" t="s">
         <v>17</v>
@@ -3538,10 +3538,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" t="s">
         <v>60</v>
-      </c>
-      <c r="B79" t="s">
-        <v>61</v>
       </c>
       <c r="C79" t="s">
         <v>16</v>
@@ -3571,10 +3571,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
         <v>16</v>
@@ -3604,10 +3604,10 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" t="s">
         <v>16</v>
@@ -3670,10 +3670,10 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C83" t="s">
         <v>16</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
         <v>16</v>

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50112438-2F2E-4E48-88C3-A79E42A3F41F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F039AF-AFFB-48AD-B26F-B4F0B0C3B4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -294,7 +294,7 @@
     <t>A5 - 115g recyclé</t>
   </si>
   <si>
-    <t>CARTE DE VISITE</t>
+    <t>Cartes de visite</t>
   </si>
 </sst>
 </file>

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F039AF-AFFB-48AD-B26F-B4F0B0C3B4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FBC7AD-1A0E-4BB4-BA85-58057DA688DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -39,31 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="85">
-  <si>
-    <t>Colonne A</t>
-  </si>
-  <si>
-    <t>Colonne B</t>
-  </si>
-  <si>
-    <t>Colonne C</t>
-  </si>
-  <si>
-    <t>Colonne D</t>
-  </si>
-  <si>
-    <t>Colonne E</t>
-  </si>
-  <si>
-    <t>Colonne F</t>
-  </si>
-  <si>
-    <t>Colonne G</t>
-  </si>
-  <si>
-    <t>Colonne H</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="77">
   <si>
     <t>Catégorie</t>
   </si>
@@ -762,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{520A29C8-9A76-4166-9594-E46298E59E8A}">
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="148.85546875" customWidth="1"/>
@@ -774,110 +750,111 @@
     <col min="11" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="D1" s="1">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>7</v>
+      <c r="F1" s="1">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1">
+        <v>50</v>
+      </c>
+      <c r="I1" s="1">
+        <v>100</v>
+      </c>
+      <c r="J1" s="1">
+        <v>250</v>
+      </c>
+      <c r="K1" s="1">
+        <v>500</v>
+      </c>
+      <c r="L1" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M1" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N1" s="1">
+        <v>5000</v>
+      </c>
+      <c r="O1" s="5">
+        <v>10000</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>25</v>
-      </c>
-      <c r="H2" s="1">
-        <v>50</v>
-      </c>
-      <c r="I2" s="1">
-        <v>100</v>
-      </c>
-      <c r="J2" s="1">
-        <v>250</v>
-      </c>
-      <c r="K2" s="1">
-        <v>500</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1">
-        <v>2500</v>
-      </c>
-      <c r="N2" s="1">
-        <v>5000</v>
-      </c>
-      <c r="O2" s="5">
-        <v>10000</v>
-      </c>
+      <c r="A2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="F2">
+        <v>7.4</v>
+      </c>
+      <c r="G2">
+        <v>5.28</v>
+      </c>
+      <c r="H2">
+        <v>4.88</v>
+      </c>
+      <c r="I2">
+        <v>4.68</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="3"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3">
-        <v>9.1999999999999993</v>
+        <v>12.8</v>
       </c>
       <c r="F3">
-        <v>7.4</v>
+        <v>10.37</v>
       </c>
       <c r="G3">
-        <v>5.28</v>
+        <v>8.6359999999999992</v>
       </c>
       <c r="H3">
-        <v>4.88</v>
+        <v>7.24</v>
       </c>
       <c r="I3">
-        <v>4.68</v>
+        <v>6.46</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -888,29 +865,29 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F4">
-        <v>10.37</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G4">
-        <v>8.6359999999999992</v>
+        <v>8.32</v>
       </c>
       <c r="H4">
-        <v>7.24</v>
+        <v>7.88</v>
       </c>
       <c r="I4">
-        <v>6.46</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -919,64 +896,64 @@
       <c r="N4" s="4"/>
       <c r="O4" s="3"/>
     </row>
-    <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D5" s="3"/>
       <c r="E5">
-        <v>12.4</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>10.199999999999999</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="G5">
-        <v>8.32</v>
+        <v>12.88</v>
       </c>
       <c r="H5">
-        <v>7.88</v>
+        <v>11.28</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
+        <v>10.36</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6">
         <v>20</v>
       </c>
       <c r="F6">
-        <v>16.399999999999999</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>12.88</v>
+        <v>14.64</v>
       </c>
       <c r="H6">
-        <v>11.28</v>
+        <v>13.8</v>
       </c>
       <c r="I6">
-        <v>10.36</v>
+        <v>13.2</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -987,29 +964,29 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7">
-        <v>20</v>
+        <v>30.4</v>
       </c>
       <c r="F7">
-        <v>17</v>
+        <v>25.6</v>
       </c>
       <c r="G7">
-        <v>14.64</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H7">
-        <v>13.8</v>
+        <v>18.68</v>
       </c>
       <c r="I7">
-        <v>13.2</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -1019,31 +996,23 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>66</v>
+      <c r="A8" t="s">
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8">
-        <v>30.4</v>
-      </c>
-      <c r="F8">
-        <v>25.6</v>
-      </c>
-      <c r="G8">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="H8">
-        <v>18.68</v>
-      </c>
-      <c r="I8">
-        <v>16.940000000000001</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>64.8</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1053,16 +1022,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>64.8</v>
+        <v>93.6</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1078,16 +1047,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>93.6</v>
+        <v>96</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1103,16 +1072,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>96</v>
+        <v>141.6</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1128,38 +1097,51 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12">
-        <v>141.6</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="I12">
+        <f>(31.35)/100</f>
+        <v>0.3135</v>
+      </c>
+      <c r="J12">
+        <v>0.13860000000000003</v>
+      </c>
+      <c r="K12">
+        <v>8.5800000000000015E-2</v>
+      </c>
+      <c r="L12">
+        <v>4.9500000000000009E-2</v>
+      </c>
+      <c r="M12">
+        <v>2.64E-2</v>
+      </c>
+      <c r="N12">
+        <v>1.8295200000000001E-2</v>
+      </c>
+      <c r="O12">
+        <v>1.4399E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1167,37 +1149,36 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13">
-        <f>(31.35)/100</f>
-        <v>0.3135</v>
+        <v>0.35200000000000004</v>
       </c>
       <c r="J13">
-        <v>0.13860000000000003</v>
+        <v>0.15180000000000002</v>
       </c>
       <c r="K13">
-        <v>8.5800000000000015E-2</v>
+        <v>9.5700000000000007E-2</v>
       </c>
       <c r="L13">
-        <v>4.9500000000000009E-2</v>
+        <v>5.2800000000000007E-2</v>
       </c>
       <c r="M13">
-        <v>2.64E-2</v>
+        <v>2.8380000000000002E-2</v>
       </c>
       <c r="N13">
-        <v>1.8295200000000001E-2</v>
+        <v>1.9650399999999998E-2</v>
       </c>
       <c r="O13">
-        <v>1.4399E-2</v>
+        <v>1.5754199999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1205,36 +1186,36 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14">
-        <v>0.35200000000000004</v>
+        <v>0.37620000000000003</v>
       </c>
       <c r="J14">
-        <v>0.15180000000000002</v>
+        <v>0.17424000000000001</v>
       </c>
       <c r="K14">
-        <v>9.5700000000000007E-2</v>
+        <v>0.11088000000000001</v>
       </c>
       <c r="L14">
-        <v>5.2800000000000007E-2</v>
+        <v>7.7220000000000011E-2</v>
       </c>
       <c r="M14">
-        <v>2.8380000000000002E-2</v>
+        <v>3.6431999999999999E-2</v>
       </c>
       <c r="N14">
-        <v>1.9650399999999998E-2</v>
+        <v>2.6716800000000002E-2</v>
       </c>
       <c r="O14">
-        <v>1.5754199999999999E-2</v>
+        <v>1.8620800000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1242,36 +1223,36 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15">
-        <v>0.37620000000000003</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="J15">
-        <v>0.17424000000000001</v>
+        <v>0.19008000000000005</v>
       </c>
       <c r="K15">
-        <v>0.11088000000000001</v>
+        <v>0.12672</v>
       </c>
       <c r="L15">
-        <v>7.7220000000000011E-2</v>
+        <v>9.3060000000000004E-2</v>
       </c>
       <c r="M15">
-        <v>3.6431999999999999E-2</v>
+        <v>4.7608000000000004E-2</v>
       </c>
       <c r="N15">
-        <v>2.6716800000000002E-2</v>
+        <v>2.87408E-2</v>
       </c>
       <c r="O15">
-        <v>1.8620800000000003E-2</v>
+        <v>2.0037599999999999E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1279,36 +1260,36 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16">
-        <v>0.39600000000000002</v>
+        <v>0.36300000000000004</v>
       </c>
       <c r="J16">
-        <v>0.19008000000000005</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="K16">
-        <v>0.12672</v>
+        <v>0.10890000000000001</v>
       </c>
       <c r="L16">
-        <v>9.3060000000000004E-2</v>
+        <v>7.7550000000000008E-2</v>
       </c>
       <c r="M16">
-        <v>4.7608000000000004E-2</v>
+        <v>4.2011200000000005E-2</v>
       </c>
       <c r="N16">
-        <v>2.87408E-2</v>
+        <v>3.32024E-2</v>
       </c>
       <c r="O16">
-        <v>2.0037599999999999E-2</v>
+        <v>2.2022E-2</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1316,36 +1297,36 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17">
-        <v>0.36300000000000004</v>
+        <v>0.3795</v>
       </c>
       <c r="J17">
-        <v>0.17160000000000003</v>
+        <v>0.19140000000000001</v>
       </c>
       <c r="K17">
-        <v>0.10890000000000001</v>
+        <v>0.12540000000000001</v>
       </c>
       <c r="L17">
-        <v>7.7550000000000008E-2</v>
+        <v>9.4864000000000004E-2</v>
       </c>
       <c r="M17">
-        <v>4.2011200000000005E-2</v>
+        <v>4.4721600000000007E-2</v>
       </c>
       <c r="N17">
-        <v>3.32024E-2</v>
+        <v>3.4896400000000008E-2</v>
       </c>
       <c r="O17">
-        <v>2.2022E-2</v>
+        <v>2.3377200000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1359,30 +1340,30 @@
         <v>0.19140000000000001</v>
       </c>
       <c r="K18">
-        <v>0.12540000000000001</v>
+        <v>0.12210000000000001</v>
       </c>
       <c r="L18">
-        <v>9.4864000000000004E-2</v>
+        <v>7.4249999999999997E-2</v>
       </c>
       <c r="M18">
-        <v>4.4721600000000007E-2</v>
+        <v>4.8787200000000003E-2</v>
       </c>
       <c r="N18">
-        <v>3.4896400000000008E-2</v>
+        <v>3.6929200000000009E-2</v>
       </c>
       <c r="O18">
-        <v>2.3377200000000001E-2</v>
+        <v>3.0661400000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1390,36 +1371,36 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19">
-        <v>0.3795</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="J19">
-        <v>0.19140000000000001</v>
+        <v>0.20460000000000003</v>
       </c>
       <c r="K19">
         <v>0.12210000000000001</v>
       </c>
       <c r="L19">
-        <v>7.4249999999999997E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
       <c r="M19">
-        <v>4.8787200000000003E-2</v>
+        <v>5.0820000000000004E-2</v>
       </c>
       <c r="N19">
-        <v>3.6929200000000009E-2</v>
+        <v>3.8284400000000003E-2</v>
       </c>
       <c r="O19">
-        <v>3.0661400000000002E-2</v>
+        <v>3.2016600000000006E-2</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1427,36 +1408,36 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20">
-        <v>0.39600000000000002</v>
+        <v>0.45539999999999997</v>
       </c>
       <c r="J20">
-        <v>0.20460000000000003</v>
+        <v>0.20592000000000002</v>
       </c>
       <c r="K20">
-        <v>0.12210000000000001</v>
+        <v>0.12276000000000001</v>
       </c>
       <c r="L20">
-        <v>7.9200000000000007E-2</v>
+        <v>8.3159999999999998E-2</v>
       </c>
       <c r="M20">
-        <v>5.0820000000000004E-2</v>
+        <v>7.4483200000000013E-2</v>
       </c>
       <c r="N20">
-        <v>3.8284400000000003E-2</v>
+        <v>4.2908800000000004E-2</v>
       </c>
       <c r="O20">
-        <v>3.2016600000000006E-2</v>
+        <v>2.8538400000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1464,22 +1445,22 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21">
-        <v>0.45539999999999997</v>
+        <v>0.47520000000000012</v>
       </c>
       <c r="J21">
-        <v>0.20592000000000002</v>
+        <v>0.22176000000000001</v>
       </c>
       <c r="K21">
-        <v>0.12276000000000001</v>
+        <v>0.14255999999999999</v>
       </c>
       <c r="L21">
-        <v>8.3159999999999998E-2</v>
+        <v>0.10524800000000002</v>
       </c>
       <c r="M21">
-        <v>7.4483200000000013E-2</v>
+        <v>7.8531199999999995E-2</v>
       </c>
       <c r="N21">
-        <v>4.2908800000000004E-2</v>
+        <v>4.6552000000000003E-2</v>
       </c>
       <c r="O21">
         <v>2.8538400000000002E-2</v>
@@ -1487,13 +1468,13 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1501,36 +1482,36 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22">
-        <v>0.47520000000000012</v>
+        <v>0.33</v>
       </c>
       <c r="J22">
-        <v>0.22176000000000001</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="K22">
-        <v>0.14255999999999999</v>
+        <v>0.11880000000000002</v>
       </c>
       <c r="L22">
-        <v>0.10524800000000002</v>
+        <v>7.2600000000000012E-2</v>
       </c>
       <c r="M22">
-        <v>7.8531199999999995E-2</v>
+        <v>4.2011200000000005E-2</v>
       </c>
       <c r="N22">
-        <v>4.6552000000000003E-2</v>
+        <v>2.74428E-2</v>
       </c>
       <c r="O22">
-        <v>2.8538400000000002E-2</v>
+        <v>2.21914E-2</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1538,36 +1519,36 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23">
-        <v>0.33</v>
+        <v>0.36300000000000004</v>
       </c>
       <c r="J23">
-        <v>0.16500000000000001</v>
+        <v>0.19140000000000001</v>
       </c>
       <c r="K23">
-        <v>0.11880000000000002</v>
+        <v>0.1353</v>
       </c>
       <c r="L23">
-        <v>7.2600000000000012E-2</v>
+        <v>8.0850000000000005E-2</v>
       </c>
       <c r="M23">
-        <v>4.2011200000000005E-2</v>
+        <v>4.6754400000000002E-2</v>
       </c>
       <c r="N23">
-        <v>2.74428E-2</v>
+        <v>3.0153200000000005E-2</v>
       </c>
       <c r="O23">
-        <v>2.21914E-2</v>
+        <v>2.4393600000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1575,36 +1556,36 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24">
-        <v>0.36300000000000004</v>
+        <v>0.41800000000000004</v>
       </c>
       <c r="J24">
-        <v>0.19140000000000001</v>
+        <v>0.19360000000000002</v>
       </c>
       <c r="K24">
-        <v>0.1353</v>
+        <v>0.1144</v>
       </c>
       <c r="L24">
-        <v>8.0850000000000005E-2</v>
+        <v>7.2600000000000012E-2</v>
       </c>
       <c r="M24">
-        <v>4.6754400000000002E-2</v>
+        <v>4.4880000000000003E-2</v>
       </c>
       <c r="N24">
-        <v>3.0153200000000005E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="O24">
-        <v>2.4393600000000001E-2</v>
+        <v>3.1899999999999998E-2</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1612,36 +1593,36 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25">
-        <v>0.41800000000000004</v>
+        <v>0.44</v>
       </c>
       <c r="J25">
-        <v>0.19360000000000002</v>
+        <v>0.23760000000000003</v>
       </c>
       <c r="K25">
-        <v>0.1144</v>
+        <v>0.13639999999999999</v>
       </c>
       <c r="L25">
-        <v>7.2600000000000012E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="M25">
-        <v>4.4880000000000003E-2</v>
+        <v>5.3680000000000005E-2</v>
       </c>
       <c r="N25">
-        <v>3.5200000000000002E-2</v>
+        <v>3.8720000000000004E-2</v>
       </c>
       <c r="O25">
-        <v>3.1899999999999998E-2</v>
+        <v>3.4759999999999999E-2</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1652,33 +1633,33 @@
         <v>0.44</v>
       </c>
       <c r="J26">
-        <v>0.23760000000000003</v>
+        <v>0.21120000000000003</v>
       </c>
       <c r="K26">
-        <v>0.13639999999999999</v>
+        <v>0.12760000000000002</v>
       </c>
       <c r="L26">
-        <v>8.7999999999999995E-2</v>
+        <v>8.3600000000000008E-2</v>
       </c>
       <c r="M26">
-        <v>5.3680000000000005E-2</v>
+        <v>5.6320000000000002E-2</v>
       </c>
       <c r="N26">
-        <v>3.8720000000000004E-2</v>
+        <v>4.9280000000000004E-2</v>
       </c>
       <c r="O26">
-        <v>3.4759999999999999E-2</v>
+        <v>4.4220000000000002E-2</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1686,36 +1667,36 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27">
-        <v>0.44</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="J27">
-        <v>0.21120000000000003</v>
+        <v>0.24640000000000004</v>
       </c>
       <c r="K27">
-        <v>0.12760000000000002</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="L27">
-        <v>8.3600000000000008E-2</v>
+        <v>0.1012</v>
       </c>
       <c r="M27">
-        <v>5.6320000000000002E-2</v>
+        <v>6.5120000000000011E-2</v>
       </c>
       <c r="N27">
-        <v>4.9280000000000004E-2</v>
+        <v>5.1040000000000002E-2</v>
       </c>
       <c r="O27">
-        <v>4.4220000000000002E-2</v>
+        <v>4.7300000000000009E-2</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C28" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1723,36 +1704,36 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28">
-        <v>0.46200000000000002</v>
+        <v>0.44550000000000006</v>
       </c>
       <c r="J28">
-        <v>0.24640000000000004</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="K28">
-        <v>0.14080000000000001</v>
+        <v>0.15840000000000001</v>
       </c>
       <c r="L28">
-        <v>0.1012</v>
+        <v>0.12196800000000001</v>
       </c>
       <c r="M28">
-        <v>6.5120000000000011E-2</v>
+        <v>7.1148000000000003E-2</v>
       </c>
       <c r="N28">
-        <v>5.1040000000000002E-2</v>
+        <v>6.67436E-2</v>
       </c>
       <c r="O28">
-        <v>4.7300000000000009E-2</v>
+        <v>6.6044000000000005E-2</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1760,36 +1741,36 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29">
-        <v>0.44550000000000006</v>
+        <v>0.47850000000000004</v>
       </c>
       <c r="J29">
-        <v>0.25080000000000002</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="K29">
-        <v>0.15840000000000001</v>
+        <v>0.182952</v>
       </c>
       <c r="L29">
-        <v>0.12196800000000001</v>
+        <v>0.132132</v>
       </c>
       <c r="M29">
-        <v>7.1148000000000003E-2</v>
+        <v>7.5891200000000006E-2</v>
       </c>
       <c r="N29">
-        <v>6.67436E-2</v>
+        <v>7.0131600000000002E-2</v>
       </c>
       <c r="O29">
-        <v>6.6044000000000005E-2</v>
+        <v>6.8824800000000005E-2</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1797,36 +1778,36 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30">
-        <v>0.47850000000000004</v>
+        <v>0.49500000000000005</v>
       </c>
       <c r="J30">
-        <v>0.26400000000000001</v>
+        <v>0.24552000000000002</v>
       </c>
       <c r="K30">
-        <v>0.182952</v>
+        <v>0.16632</v>
       </c>
       <c r="L30">
-        <v>0.132132</v>
+        <v>9.5040000000000027E-2</v>
       </c>
       <c r="M30">
-        <v>7.5891200000000006E-2</v>
+        <v>8.3388800000000013E-2</v>
       </c>
       <c r="N30">
-        <v>7.0131600000000002E-2</v>
+        <v>6.1124800000000007E-2</v>
       </c>
       <c r="O30">
-        <v>6.8824800000000005E-2</v>
+        <v>4.9588000000000007E-2</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1834,36 +1815,36 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31">
-        <v>0.49500000000000005</v>
+        <v>0.53460000000000008</v>
       </c>
       <c r="J31">
-        <v>0.24552000000000002</v>
+        <v>0.28511999999999998</v>
       </c>
       <c r="K31">
-        <v>0.16632</v>
+        <v>0.21049600000000004</v>
       </c>
       <c r="L31">
-        <v>9.5040000000000027E-2</v>
+        <v>0.13560800000000001</v>
       </c>
       <c r="M31">
-        <v>8.3388800000000013E-2</v>
+        <v>9.1484800000000005E-2</v>
       </c>
       <c r="N31">
-        <v>6.1124800000000007E-2</v>
+        <v>6.6387200000000007E-2</v>
       </c>
       <c r="O31">
-        <v>4.9588000000000007E-2</v>
+        <v>5.3028800000000001E-2</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1871,36 +1852,36 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32">
-        <v>0.53460000000000008</v>
+        <v>0.57200000000000006</v>
       </c>
       <c r="J32">
-        <v>0.28511999999999998</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="K32">
-        <v>0.21049600000000004</v>
+        <v>0.17160000000000003</v>
       </c>
       <c r="L32">
-        <v>0.13560800000000001</v>
+        <v>9.4600000000000004E-2</v>
       </c>
       <c r="M32">
-        <v>9.1484800000000005E-2</v>
+        <v>5.8080000000000007E-2</v>
       </c>
       <c r="N32">
-        <v>6.6387200000000007E-2</v>
+        <v>4.2240000000000007E-2</v>
       </c>
       <c r="O32">
-        <v>5.3028800000000001E-2</v>
+        <v>3.6520000000000004E-2</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1908,36 +1889,36 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33">
-        <v>0.57200000000000006</v>
+        <v>0.6160000000000001</v>
       </c>
       <c r="J33">
-        <v>0.31680000000000003</v>
+        <v>0.34320000000000006</v>
       </c>
       <c r="K33">
-        <v>0.17160000000000003</v>
+        <v>0.18920000000000001</v>
       </c>
       <c r="L33">
-        <v>9.4600000000000004E-2</v>
+        <v>0.10340000000000001</v>
       </c>
       <c r="M33">
-        <v>5.8080000000000007E-2</v>
+        <v>6.6880000000000009E-2</v>
       </c>
       <c r="N33">
-        <v>4.2240000000000007E-2</v>
+        <v>5.8520000000000003E-2</v>
       </c>
       <c r="O33">
-        <v>3.6520000000000004E-2</v>
+        <v>5.0820000000000004E-2</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1945,36 +1926,36 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34">
-        <v>0.6160000000000001</v>
+        <v>0.81400000000000006</v>
       </c>
       <c r="J34">
-        <v>0.34320000000000006</v>
+        <v>0.43120000000000003</v>
       </c>
       <c r="K34">
-        <v>0.18920000000000001</v>
+        <v>0.25520000000000004</v>
       </c>
       <c r="L34">
-        <v>0.10340000000000001</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="M34">
-        <v>6.6880000000000009E-2</v>
+        <v>9.1520000000000004E-2</v>
       </c>
       <c r="N34">
-        <v>5.8520000000000003E-2</v>
+        <v>8.8000000000000009E-2</v>
       </c>
       <c r="O34">
-        <v>5.0820000000000004E-2</v>
+        <v>7.6560000000000003E-2</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1982,36 +1963,36 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35">
-        <v>0.81400000000000006</v>
+        <v>0.77</v>
       </c>
       <c r="J35">
-        <v>0.43120000000000003</v>
+        <v>0.44880000000000003</v>
       </c>
       <c r="K35">
-        <v>0.25520000000000004</v>
+        <v>0.29040000000000005</v>
       </c>
       <c r="L35">
-        <v>0.14080000000000001</v>
+        <v>0.18480000000000002</v>
       </c>
       <c r="M35">
-        <v>9.1520000000000004E-2</v>
+        <v>9.6800000000000011E-2</v>
       </c>
       <c r="N35">
-        <v>8.8000000000000009E-2</v>
+        <v>8.4920000000000009E-2</v>
       </c>
       <c r="O35">
-        <v>7.6560000000000003E-2</v>
+        <v>8.3600000000000008E-2</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2022,33 +2003,33 @@
         <v>0.77</v>
       </c>
       <c r="J36">
-        <v>0.44880000000000003</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="K36">
-        <v>0.29040000000000005</v>
+        <v>0.20680000000000001</v>
       </c>
       <c r="L36">
-        <v>0.18480000000000002</v>
+        <v>0.12100000000000001</v>
       </c>
       <c r="M36">
-        <v>9.6800000000000011E-2</v>
+        <v>8.7120000000000003E-2</v>
       </c>
       <c r="N36">
-        <v>8.4920000000000009E-2</v>
+        <v>5.9840000000000011E-2</v>
       </c>
       <c r="O36">
-        <v>8.3600000000000008E-2</v>
+        <v>5.4560000000000004E-2</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2056,36 +2037,36 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37">
-        <v>0.77</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="J37">
-        <v>0.36960000000000004</v>
+        <v>0.43120000000000003</v>
       </c>
       <c r="K37">
-        <v>0.20680000000000001</v>
+        <v>0.24640000000000004</v>
       </c>
       <c r="L37">
-        <v>0.12100000000000001</v>
+        <v>0.14960000000000001</v>
       </c>
       <c r="M37">
-        <v>8.7120000000000003E-2</v>
+        <v>0.1144</v>
       </c>
       <c r="N37">
-        <v>5.9840000000000011E-2</v>
+        <v>8.7559999999999999E-2</v>
       </c>
       <c r="O37">
-        <v>5.4560000000000004E-2</v>
+        <v>6.9960000000000008E-2</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2093,36 +2074,36 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38">
-        <v>0.79200000000000004</v>
+        <v>0.88</v>
       </c>
       <c r="J38">
-        <v>0.43120000000000003</v>
+        <v>0.44880000000000003</v>
       </c>
       <c r="K38">
-        <v>0.24640000000000004</v>
+        <v>0.25080000000000002</v>
       </c>
       <c r="L38">
-        <v>0.14960000000000001</v>
+        <v>0.1628</v>
       </c>
       <c r="M38">
-        <v>0.1144</v>
+        <v>0.13376000000000002</v>
       </c>
       <c r="N38">
-        <v>8.7559999999999999E-2</v>
+        <v>0.10164000000000001</v>
       </c>
       <c r="O38">
-        <v>6.9960000000000008E-2</v>
+        <v>9.8119999999999999E-2</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -2130,36 +2111,36 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39">
-        <v>0.88</v>
+        <v>0.96800000000000008</v>
       </c>
       <c r="J39">
-        <v>0.44880000000000003</v>
+        <v>0.58080000000000009</v>
       </c>
       <c r="K39">
-        <v>0.25080000000000002</v>
+        <v>0.36960000000000004</v>
       </c>
       <c r="L39">
-        <v>0.1628</v>
+        <v>0.22000000000000003</v>
       </c>
       <c r="M39">
-        <v>0.13376000000000002</v>
+        <v>0.16984000000000002</v>
       </c>
       <c r="N39">
-        <v>0.10164000000000001</v>
+        <v>0.18084</v>
       </c>
       <c r="O39">
-        <v>9.8119999999999999E-2</v>
+        <v>0.13134000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -2167,36 +2148,36 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40">
-        <v>0.96800000000000008</v>
+        <v>0.88</v>
       </c>
       <c r="J40">
         <v>0.58080000000000009</v>
       </c>
       <c r="K40">
-        <v>0.36960000000000004</v>
+        <v>0.33440000000000003</v>
       </c>
       <c r="L40">
-        <v>0.22000000000000003</v>
+        <v>0.1958</v>
       </c>
       <c r="M40">
-        <v>0.16984000000000002</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="N40">
-        <v>0.18084</v>
+        <v>0.121</v>
       </c>
       <c r="O40">
-        <v>0.13134000000000001</v>
+        <v>0.10142000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -2204,36 +2185,36 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41">
-        <v>0.88</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="J41">
-        <v>0.58080000000000009</v>
+        <v>0.67759999999999998</v>
       </c>
       <c r="K41">
-        <v>0.33440000000000003</v>
+        <v>0.40040000000000003</v>
       </c>
       <c r="L41">
-        <v>0.1958</v>
+        <v>0.253</v>
       </c>
       <c r="M41">
-        <v>0.14080000000000001</v>
+        <v>0.20856000000000002</v>
       </c>
       <c r="N41">
-        <v>0.121</v>
+        <v>0.16324</v>
       </c>
       <c r="O41">
-        <v>0.10142000000000001</v>
+        <v>0.14630000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -2241,36 +2222,36 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42">
-        <v>0.92400000000000004</v>
+        <v>0.96800000000000008</v>
       </c>
       <c r="J42">
         <v>0.67759999999999998</v>
       </c>
       <c r="K42">
-        <v>0.40040000000000003</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="L42">
-        <v>0.253</v>
+        <v>0.29040000000000005</v>
       </c>
       <c r="M42">
-        <v>0.20856000000000002</v>
+        <v>0.26752000000000004</v>
       </c>
       <c r="N42">
-        <v>0.16324</v>
+        <v>0.25740000000000002</v>
       </c>
       <c r="O42">
-        <v>0.14630000000000001</v>
+        <v>0.19822000000000004</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -2278,36 +2259,36 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43">
-        <v>0.96800000000000008</v>
+        <v>1.32</v>
       </c>
       <c r="J43">
-        <v>0.67759999999999998</v>
+        <v>0.73920000000000008</v>
       </c>
       <c r="K43">
         <v>0.44000000000000006</v>
       </c>
       <c r="L43">
-        <v>0.29040000000000005</v>
+        <v>0.33879999999999999</v>
       </c>
       <c r="M43">
-        <v>0.26752000000000004</v>
+        <v>0.36168</v>
       </c>
       <c r="N43">
-        <v>0.25740000000000002</v>
+        <v>0.26268000000000002</v>
       </c>
       <c r="O43">
-        <v>0.19822000000000004</v>
+        <v>0.15114</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -2315,36 +2296,36 @@
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44">
-        <v>1.32</v>
+        <v>1.4960000000000002</v>
       </c>
       <c r="J44">
-        <v>0.73920000000000008</v>
+        <v>0.84480000000000011</v>
       </c>
       <c r="K44">
-        <v>0.44000000000000006</v>
+        <v>0.51480000000000004</v>
       </c>
       <c r="L44">
-        <v>0.33879999999999999</v>
+        <v>0.32120000000000004</v>
       </c>
       <c r="M44">
-        <v>0.36168</v>
+        <v>0.23584000000000002</v>
       </c>
       <c r="N44">
-        <v>0.26268000000000002</v>
+        <v>0.16016000000000002</v>
       </c>
       <c r="O44">
-        <v>0.15114</v>
+        <v>0.15290000000000004</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -2352,36 +2333,36 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45">
-        <v>1.4960000000000002</v>
+        <v>1.5620000000000003</v>
       </c>
       <c r="J45">
-        <v>0.84480000000000011</v>
+        <v>0.91520000000000001</v>
       </c>
       <c r="K45">
-        <v>0.51480000000000004</v>
+        <v>0.55440000000000011</v>
       </c>
       <c r="L45">
-        <v>0.32120000000000004</v>
+        <v>0.43780000000000002</v>
       </c>
       <c r="M45">
-        <v>0.23584000000000002</v>
+        <v>0.29480000000000006</v>
       </c>
       <c r="N45">
-        <v>0.16016000000000002</v>
+        <v>0.22308000000000003</v>
       </c>
       <c r="O45">
-        <v>0.15290000000000004</v>
+        <v>0.20482000000000003</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2389,94 +2370,92 @@
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46">
-        <v>1.5620000000000003</v>
+        <v>1.4520000000000002</v>
       </c>
       <c r="J46">
-        <v>0.91520000000000001</v>
+        <v>0.80080000000000007</v>
       </c>
       <c r="K46">
-        <v>0.55440000000000011</v>
+        <v>0.49720000000000003</v>
       </c>
       <c r="L46">
-        <v>0.43780000000000002</v>
+        <v>0.43560000000000004</v>
       </c>
       <c r="M46">
-        <v>0.29480000000000006</v>
+        <v>0.41360000000000002</v>
       </c>
       <c r="N46">
-        <v>0.22308000000000003</v>
+        <v>0.29436000000000001</v>
       </c>
       <c r="O46">
-        <v>0.20482000000000003</v>
+        <v>0.15906000000000001</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
+      <c r="G47">
+        <v>4.7520000000000007</v>
+      </c>
+      <c r="H47">
+        <v>2.9304000000000001</v>
+      </c>
       <c r="I47">
-        <v>1.4520000000000002</v>
+        <v>1.8414000000000001</v>
       </c>
       <c r="J47">
-        <v>0.80080000000000007</v>
+        <v>1.2117599999999999</v>
       </c>
       <c r="K47">
-        <v>0.49720000000000003</v>
+        <v>1.0573200000000003</v>
       </c>
       <c r="L47">
-        <v>0.43560000000000004</v>
-      </c>
-      <c r="M47">
-        <v>0.41360000000000002</v>
-      </c>
-      <c r="N47">
-        <v>0.29436000000000001</v>
-      </c>
-      <c r="O47">
-        <v>0.15906000000000001</v>
-      </c>
+        <v>0.98850400000000005</v>
+      </c>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48">
-        <v>4.7520000000000007</v>
+        <v>5.8608000000000002</v>
       </c>
       <c r="H48">
-        <v>2.9304000000000001</v>
+        <v>3.6431999999999998</v>
       </c>
       <c r="I48">
-        <v>1.8414000000000001</v>
+        <v>2.5542000000000002</v>
       </c>
       <c r="J48">
-        <v>1.2117599999999999</v>
+        <v>2.0829599999999999</v>
       </c>
       <c r="K48">
-        <v>1.0573200000000003</v>
+        <v>1.9479680000000004</v>
       </c>
       <c r="L48">
-        <v>0.98850400000000005</v>
+        <v>1.7929560000000002</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -2484,34 +2463,34 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49">
-        <v>5.8608000000000002</v>
+        <v>7.3656000000000006</v>
       </c>
       <c r="H49">
-        <v>3.6431999999999998</v>
+        <v>5.1084000000000005</v>
       </c>
       <c r="I49">
-        <v>2.5542000000000002</v>
+        <v>4.3163999999999998</v>
       </c>
       <c r="J49">
-        <v>2.0829599999999999</v>
+        <v>3.8712960000000001</v>
       </c>
       <c r="K49">
-        <v>1.9479680000000004</v>
+        <v>3.5610960000000005</v>
       </c>
       <c r="L49">
-        <v>1.7929560000000002</v>
+        <v>3.4969880000000004</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -2519,59 +2498,67 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
+      <c r="F50">
+        <v>4.136000000000001</v>
+      </c>
       <c r="G50">
-        <v>7.3656000000000006</v>
+        <v>2.31616</v>
       </c>
       <c r="H50">
-        <v>5.1084000000000005</v>
+        <v>1.5303200000000001</v>
       </c>
       <c r="I50">
-        <v>4.3163999999999998</v>
+        <v>1.1167200000000002</v>
       </c>
       <c r="J50">
-        <v>3.8712960000000001</v>
+        <v>0.50459200000000015</v>
       </c>
       <c r="K50">
-        <v>3.5610960000000005</v>
+        <v>0.28952000000000006</v>
       </c>
       <c r="L50">
-        <v>3.4969880000000004</v>
-      </c>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+        <v>0.18405200000000002</v>
+      </c>
+      <c r="M50">
+        <v>0.13752200000000003</v>
+      </c>
+      <c r="N50">
+        <v>0.112706</v>
+      </c>
+      <c r="O50">
+        <v>0.10009120000000001</v>
+      </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51">
-        <v>4.136000000000001</v>
+        <v>4.3427999999999995</v>
       </c>
       <c r="G51">
-        <v>2.31616</v>
+        <v>2.3988800000000001</v>
       </c>
       <c r="H51">
-        <v>1.5303200000000001</v>
+        <v>1.61304</v>
       </c>
       <c r="I51">
         <v>1.1167200000000002</v>
@@ -2580,364 +2567,352 @@
         <v>0.50459200000000015</v>
       </c>
       <c r="K51">
-        <v>0.28952000000000006</v>
+        <v>0.29365600000000003</v>
       </c>
       <c r="L51">
-        <v>0.18405200000000002</v>
+        <v>0.18612000000000001</v>
       </c>
       <c r="M51">
         <v>0.13752200000000003</v>
       </c>
       <c r="N51">
-        <v>0.112706</v>
+        <v>0.11891</v>
       </c>
       <c r="O51">
-        <v>0.10009120000000001</v>
+        <v>0.11063800000000001</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52">
-        <v>4.3427999999999995</v>
+        <v>4.5495999999999999</v>
       </c>
       <c r="G52">
-        <v>2.3988800000000001</v>
+        <v>2.8952000000000004</v>
       </c>
       <c r="H52">
-        <v>1.61304</v>
+        <v>1.9439200000000003</v>
       </c>
       <c r="I52">
-        <v>1.1167200000000002</v>
+        <v>1.32352</v>
       </c>
       <c r="J52">
-        <v>0.50459200000000015</v>
+        <v>0.58731200000000006</v>
       </c>
       <c r="K52">
-        <v>0.29365600000000003</v>
+        <v>0.34742399999999996</v>
       </c>
       <c r="L52">
-        <v>0.18612000000000001</v>
+        <v>0.22334400000000001</v>
       </c>
       <c r="M52">
-        <v>0.13752200000000003</v>
+        <v>0.172678</v>
       </c>
       <c r="N52">
-        <v>0.11891</v>
+        <v>0.13958999999999999</v>
       </c>
       <c r="O52">
-        <v>0.11063800000000001</v>
+        <v>0.12242560000000001</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B53" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>31.680000000000003</v>
+      </c>
+      <c r="E53">
+        <v>6.3360000000000003</v>
+      </c>
       <c r="F53">
-        <v>4.5495999999999999</v>
+        <v>3.1680000000000001</v>
       </c>
       <c r="G53">
-        <v>2.8952000000000004</v>
+        <v>1.2672000000000001</v>
       </c>
       <c r="H53">
-        <v>1.9439200000000003</v>
+        <v>0.63360000000000005</v>
       </c>
       <c r="I53">
-        <v>1.32352</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="J53">
-        <v>0.58731200000000006</v>
+        <v>0.21824000000000005</v>
       </c>
       <c r="K53">
-        <v>0.34742399999999996</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="L53">
-        <v>0.22334400000000001</v>
+        <v>0.12903000000000001</v>
       </c>
       <c r="M53">
-        <v>0.172678</v>
-      </c>
-      <c r="N53">
-        <v>0.13958999999999999</v>
-      </c>
-      <c r="O53">
-        <v>0.12242560000000001</v>
-      </c>
+        <v>0.11444400000000003</v>
+      </c>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D54">
-        <v>31.680000000000003</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="E54">
-        <v>6.3360000000000003</v>
+        <v>12.320000000000002</v>
       </c>
       <c r="F54">
-        <v>3.1680000000000001</v>
+        <v>6.160000000000001</v>
       </c>
       <c r="G54">
-        <v>1.2672000000000001</v>
+        <v>2.4640000000000004</v>
       </c>
       <c r="H54">
-        <v>0.63360000000000005</v>
+        <v>1.2320000000000002</v>
       </c>
       <c r="I54">
-        <v>0.3696000000000001</v>
+        <v>0.82720000000000016</v>
       </c>
       <c r="J54">
-        <v>0.21824000000000005</v>
+        <v>0.74800000000000011</v>
       </c>
       <c r="K54">
-        <v>0.14080000000000001</v>
+        <v>0.68067999999999995</v>
       </c>
       <c r="L54">
-        <v>0.12903000000000001</v>
+        <v>0.68112000000000017</v>
       </c>
       <c r="M54">
-        <v>0.11444400000000003</v>
+        <v>0.65736000000000006</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>61.600000000000009</v>
+        <v>46.2</v>
       </c>
       <c r="E55">
-        <v>12.320000000000002</v>
+        <v>12.760000000000002</v>
       </c>
       <c r="F55">
-        <v>6.160000000000001</v>
+        <v>8.3600000000000012</v>
       </c>
       <c r="G55">
-        <v>2.4640000000000004</v>
+        <v>4.048</v>
       </c>
       <c r="H55">
-        <v>1.2320000000000002</v>
+        <v>2.7280000000000002</v>
       </c>
       <c r="I55">
-        <v>0.82720000000000016</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="J55">
-        <v>0.74800000000000011</v>
+        <v>1.9360000000000002</v>
       </c>
       <c r="K55">
-        <v>0.68067999999999995</v>
-      </c>
-      <c r="L55">
-        <v>0.68112000000000017</v>
-      </c>
-      <c r="M55">
-        <v>0.65736000000000006</v>
-      </c>
+        <v>1.6280000000000003</v>
+      </c>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D56">
-        <v>46.2</v>
+        <v>31.680000000000003</v>
       </c>
       <c r="E56">
-        <v>12.760000000000002</v>
+        <v>6.3360000000000003</v>
       </c>
       <c r="F56">
-        <v>8.3600000000000012</v>
+        <v>3.1680000000000001</v>
       </c>
       <c r="G56">
-        <v>4.048</v>
+        <v>1.2672000000000001</v>
       </c>
       <c r="H56">
-        <v>2.7280000000000002</v>
+        <v>0.63360000000000005</v>
       </c>
       <c r="I56">
-        <v>2.3540000000000001</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="J56">
-        <v>1.9360000000000002</v>
+        <v>0.21824000000000005</v>
       </c>
       <c r="K56">
-        <v>1.6280000000000003</v>
-      </c>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
+        <v>0.14080000000000001</v>
+      </c>
+      <c r="L56">
+        <v>0.12903000000000001</v>
+      </c>
+      <c r="M56">
+        <v>0.11444400000000003</v>
+      </c>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D57">
-        <v>31.680000000000003</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="E57">
-        <v>6.3360000000000003</v>
+        <v>14.080000000000002</v>
       </c>
       <c r="F57">
-        <v>3.1680000000000001</v>
+        <v>7.0400000000000009</v>
       </c>
       <c r="G57">
-        <v>1.2672000000000001</v>
+        <v>2.8160000000000003</v>
       </c>
       <c r="H57">
-        <v>0.63360000000000005</v>
+        <v>1.4080000000000001</v>
       </c>
       <c r="I57">
-        <v>0.3696000000000001</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="J57">
-        <v>0.21824000000000005</v>
+        <v>0.51612000000000002</v>
       </c>
       <c r="K57">
-        <v>0.14080000000000001</v>
+        <v>0.46002000000000004</v>
       </c>
       <c r="L57">
-        <v>0.12903000000000001</v>
-      </c>
-      <c r="M57">
-        <v>0.11444400000000003</v>
-      </c>
+        <v>0.43571000000000004</v>
+      </c>
+      <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D58">
-        <v>70.400000000000006</v>
+        <v>129.03</v>
       </c>
       <c r="E58">
-        <v>14.080000000000002</v>
+        <v>12.760000000000002</v>
       </c>
       <c r="F58">
-        <v>7.0400000000000009</v>
+        <v>8.3600000000000012</v>
       </c>
       <c r="G58">
-        <v>2.8160000000000003</v>
+        <v>4.048</v>
       </c>
       <c r="H58">
-        <v>1.4080000000000001</v>
+        <v>2.7280000000000002</v>
       </c>
       <c r="I58">
-        <v>0.99109999999999998</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="J58">
-        <v>0.51612000000000002</v>
+        <v>1.9360000000000002</v>
       </c>
       <c r="K58">
-        <v>0.46002000000000004</v>
-      </c>
-      <c r="L58">
-        <v>0.43571000000000004</v>
-      </c>
+        <v>1.6280000000000003</v>
+      </c>
+      <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59">
-        <v>129.03</v>
-      </c>
-      <c r="E59">
-        <v>12.760000000000002</v>
-      </c>
-      <c r="F59">
-        <v>8.3600000000000012</v>
-      </c>
-      <c r="G59">
-        <v>4.048</v>
-      </c>
-      <c r="H59">
-        <v>2.7280000000000002</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
       <c r="I59">
-        <v>2.3540000000000001</v>
+        <v>0.19899999999999998</v>
       </c>
       <c r="J59">
-        <v>1.9360000000000002</v>
+        <v>0.1196</v>
       </c>
       <c r="K59">
-        <v>1.6280000000000003</v>
-      </c>
-      <c r="L59" s="3"/>
+        <v>7.9799999999999996E-2</v>
+      </c>
+      <c r="L59">
+        <v>4.5899999999999996E-2</v>
+      </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2945,16 +2920,16 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60">
-        <v>0.19899999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="J60">
-        <v>0.1196</v>
+        <v>0.15959999999999999</v>
       </c>
       <c r="K60">
-        <v>7.9799999999999996E-2</v>
+        <v>9.98E-2</v>
       </c>
       <c r="L60">
-        <v>4.5899999999999996E-2</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
@@ -2962,13 +2937,13 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2976,16 +2951,16 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61">
-        <v>0.29899999999999999</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="J61">
-        <v>0.15959999999999999</v>
+        <v>0.18359999999999999</v>
       </c>
       <c r="K61">
-        <v>9.98E-2</v>
+        <v>0.1118</v>
       </c>
       <c r="L61">
-        <v>5.9900000000000002E-2</v>
+        <v>6.4899999999999999E-2</v>
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
@@ -2993,13 +2968,13 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3007,30 +2982,30 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62">
-        <v>0.34899999999999998</v>
+        <v>0.39899999999999997</v>
       </c>
       <c r="J62">
-        <v>0.18359999999999999</v>
+        <v>0.1996</v>
       </c>
       <c r="K62">
-        <v>0.1118</v>
+        <v>0.1198</v>
       </c>
       <c r="L62">
-        <v>6.4899999999999999E-2</v>
+        <v>6.9900000000000004E-2</v>
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>84</v>
+      <c r="A63" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3038,30 +3013,34 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63">
-        <v>0.39899999999999997</v>
+        <v>0.4536</v>
       </c>
       <c r="J63">
-        <v>0.1996</v>
+        <v>0.29959199999999997</v>
       </c>
       <c r="K63">
-        <v>0.1198</v>
+        <v>0.247032</v>
       </c>
       <c r="L63">
-        <v>6.9900000000000004E-2</v>
-      </c>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
+        <v>0.1764</v>
+      </c>
+      <c r="M63">
+        <v>8.3044800000000016E-2</v>
+      </c>
+      <c r="N63">
+        <v>7.3583999999999997E-2</v>
+      </c>
       <c r="O63" s="3"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3069,34 +3048,34 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64">
-        <v>0.4536</v>
+        <v>0.3528</v>
       </c>
       <c r="J64">
-        <v>0.29959199999999997</v>
+        <v>0.2016</v>
       </c>
       <c r="K64">
-        <v>0.247032</v>
+        <v>0.14716799999999999</v>
       </c>
       <c r="L64">
-        <v>0.1764</v>
+        <v>0.12220200000000001</v>
       </c>
       <c r="M64">
-        <v>8.3044800000000016E-2</v>
+        <v>5.0457600000000005E-2</v>
       </c>
       <c r="N64">
-        <v>7.3583999999999997E-2</v>
+        <v>3.9682800000000004E-2</v>
       </c>
       <c r="O64" s="3"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C65" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3104,34 +3083,34 @@
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65">
-        <v>0.3528</v>
+        <v>0.3024</v>
       </c>
       <c r="J65">
-        <v>0.2016</v>
+        <v>0.14615999999999998</v>
       </c>
       <c r="K65">
-        <v>0.14716799999999999</v>
+        <v>9.8280000000000006E-2</v>
       </c>
       <c r="L65">
-        <v>0.12220200000000001</v>
+        <v>7.7525999999999998E-2</v>
       </c>
       <c r="M65">
-        <v>5.0457600000000005E-2</v>
+        <v>3.4164000000000007E-2</v>
       </c>
       <c r="N65">
-        <v>3.9682800000000004E-2</v>
+        <v>2.7068400000000003E-2</v>
       </c>
       <c r="O65" s="3"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3139,34 +3118,40 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66">
-        <v>0.3024</v>
+        <f>(37*(0.85*2))/100</f>
+        <v>0.629</v>
       </c>
       <c r="J66">
-        <v>0.14615999999999998</v>
+        <f>(74*(0.85*2))/250</f>
+        <v>0.50319999999999998</v>
       </c>
       <c r="K66">
-        <v>9.8280000000000006E-2</v>
+        <f>(99*(0.85*2))/500</f>
+        <v>0.33659999999999995</v>
       </c>
       <c r="L66">
-        <v>7.7525999999999998E-2</v>
+        <f>(139*(0.85*2))/1000</f>
+        <v>0.23629999999999998</v>
       </c>
       <c r="M66">
-        <v>3.4164000000000007E-2</v>
+        <f>(265*(0.85*2))/2500</f>
+        <v>0.1802</v>
       </c>
       <c r="N66">
-        <v>2.7068400000000003E-2</v>
+        <f>(481*(0.85*2))/5000</f>
+        <v>0.16353999999999999</v>
       </c>
       <c r="O66" s="3"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C67" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -3174,98 +3159,82 @@
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67">
-        <f>(37*(0.85*2))/100</f>
-        <v>0.629</v>
+        <f>(27*(0.85*2))/100</f>
+        <v>0.45899999999999996</v>
       </c>
       <c r="J67">
-        <f>(74*(0.85*2))/250</f>
-        <v>0.50319999999999998</v>
+        <f>(40*(0.85*2))/250</f>
+        <v>0.27200000000000002</v>
       </c>
       <c r="K67">
-        <f>(99*(0.85*2))/500</f>
-        <v>0.33659999999999995</v>
+        <f>(48*(0.85*2))/500</f>
+        <v>0.16319999999999998</v>
       </c>
       <c r="L67">
-        <f>(139*(0.85*2))/1000</f>
-        <v>0.23629999999999998</v>
+        <f>(66*(0.85*2))/1000</f>
+        <v>0.11220000000000001</v>
       </c>
       <c r="M67">
-        <f>(265*(0.85*2))/2500</f>
-        <v>0.1802</v>
+        <f>(122*(0.85*2))/2500</f>
+        <v>8.2960000000000006E-2</v>
       </c>
       <c r="N67">
-        <f>(481*(0.85*2))/5000</f>
-        <v>0.16353999999999999</v>
+        <f>(213*(0.85*2))/5000</f>
+        <v>7.2419999999999998E-2</v>
       </c>
       <c r="O67" s="3"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" t="s">
-        <v>44</v>
+        <v>33</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
+      <c r="H68">
+        <v>2.16</v>
+      </c>
       <c r="I68">
-        <f>(27*(0.85*2))/100</f>
-        <v>0.45899999999999996</v>
+        <v>1.72</v>
       </c>
       <c r="J68">
-        <f>(40*(0.85*2))/250</f>
-        <v>0.27200000000000002</v>
+        <v>1.51</v>
       </c>
       <c r="K68">
-        <f>(48*(0.85*2))/500</f>
-        <v>0.16319999999999998</v>
-      </c>
-      <c r="L68">
-        <f>(66*(0.85*2))/1000</f>
-        <v>0.11220000000000001</v>
-      </c>
-      <c r="M68">
-        <f>(122*(0.85*2))/2500</f>
-        <v>8.2960000000000006E-2</v>
-      </c>
-      <c r="N68">
-        <f>(213*(0.85*2))/5000</f>
-        <v>7.2419999999999998E-2</v>
-      </c>
+        <v>1.26</v>
+      </c>
+      <c r="L68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
       <c r="O68" s="3"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>47</v>
+      <c r="A69" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" t="s">
+        <v>40</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
-      </c>
-      <c r="D69" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="D69">
+        <v>75.375</v>
+      </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
-      <c r="H69">
-        <v>2.16</v>
-      </c>
-      <c r="I69">
-        <v>1.72</v>
-      </c>
-      <c r="J69">
-        <v>1.51</v>
-      </c>
-      <c r="K69">
-        <v>1.26</v>
-      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -3273,16 +3242,16 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D70">
-        <v>75.375</v>
+        <v>87.5</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -3298,16 +3267,16 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D71">
-        <v>87.5</v>
+        <v>124.25</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -3323,16 +3292,16 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D72">
-        <v>124.25</v>
+        <v>150.5</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -3348,16 +3317,16 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D73">
-        <v>150.5</v>
+        <v>176.75</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -3373,38 +3342,48 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B74" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74">
-        <v>176.75</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
+      <c r="I74">
+        <v>0.96800000000000008</v>
+      </c>
+      <c r="J74">
+        <v>0.74800000000000011</v>
+      </c>
+      <c r="K74">
+        <v>0.62480000000000002</v>
+      </c>
+      <c r="L74">
+        <v>0.5918000000000001</v>
+      </c>
+      <c r="M74">
+        <v>0.45408000000000004</v>
+      </c>
+      <c r="N74">
+        <v>0.35376000000000002</v>
+      </c>
       <c r="O74" s="3"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3412,34 +3391,34 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75">
-        <v>0.96800000000000008</v>
+        <v>1.254</v>
       </c>
       <c r="J75">
-        <v>0.74800000000000011</v>
+        <v>1.1176000000000001</v>
       </c>
       <c r="K75">
-        <v>0.62480000000000002</v>
+        <v>0.9284</v>
       </c>
       <c r="L75">
-        <v>0.5918000000000001</v>
+        <v>0.78980000000000006</v>
       </c>
       <c r="M75">
-        <v>0.45408000000000004</v>
+        <v>0.54032000000000002</v>
       </c>
       <c r="N75">
-        <v>0.35376000000000002</v>
+        <v>0.41095999999999999</v>
       </c>
       <c r="O75" s="3"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3447,34 +3426,34 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76">
-        <v>1.254</v>
+        <v>1.034</v>
       </c>
       <c r="J76">
-        <v>1.1176000000000001</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="K76">
-        <v>0.9284</v>
+        <v>0.66</v>
       </c>
       <c r="L76">
-        <v>0.78980000000000006</v>
+        <v>0.62260000000000004</v>
       </c>
       <c r="M76">
-        <v>0.54032000000000002</v>
+        <v>0.52888000000000002</v>
       </c>
       <c r="N76">
-        <v>0.41095999999999999</v>
+        <v>0.38324000000000003</v>
       </c>
       <c r="O76" s="3"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3482,88 +3461,86 @@
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
       <c r="I77">
-        <v>1.034</v>
+        <v>1.3420000000000001</v>
       </c>
       <c r="J77">
-        <v>0.79200000000000004</v>
+        <v>1.1792000000000002</v>
       </c>
       <c r="K77">
-        <v>0.66</v>
+        <v>0.98120000000000007</v>
       </c>
       <c r="L77">
-        <v>0.62260000000000004</v>
+        <v>0.83600000000000008</v>
       </c>
       <c r="M77">
-        <v>0.52888000000000002</v>
+        <v>0.5684800000000001</v>
       </c>
       <c r="N77">
-        <v>0.38324000000000003</v>
+        <v>0.44703999999999999</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
+      <c r="H78">
+        <v>1.1760000000000002</v>
+      </c>
       <c r="I78">
-        <v>1.3420000000000001</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="J78">
-        <v>1.1792000000000002</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="K78">
-        <v>0.98120000000000007</v>
+        <v>0.56700000000000006</v>
       </c>
       <c r="L78">
-        <v>0.83600000000000008</v>
-      </c>
-      <c r="M78">
-        <v>0.5684800000000001</v>
-      </c>
-      <c r="N78">
-        <v>0.44703999999999999</v>
-      </c>
+        <v>0.56700000000000006</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
       <c r="O78" s="3"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79">
-        <v>1.1760000000000002</v>
+        <v>1.6380000000000001</v>
       </c>
       <c r="I79">
-        <v>0.73499999999999999</v>
+        <v>1.1130000000000002</v>
       </c>
       <c r="J79">
-        <v>0.60899999999999999</v>
+        <v>1.0710000000000002</v>
       </c>
       <c r="K79">
-        <v>0.56700000000000006</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="L79">
-        <v>0.56700000000000006</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -3571,32 +3548,32 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80">
-        <v>1.6380000000000001</v>
+        <v>2.3520000000000003</v>
       </c>
       <c r="I80">
-        <v>1.1130000000000002</v>
+        <v>1.3230000000000002</v>
       </c>
       <c r="J80">
+        <v>1.1760000000000002</v>
+      </c>
+      <c r="K80">
         <v>1.0710000000000002</v>
       </c>
-      <c r="K80">
-        <v>0.98699999999999999</v>
-      </c>
       <c r="L80">
-        <v>0.92400000000000004</v>
+        <v>1.05</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -3604,32 +3581,32 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81">
-        <v>2.3520000000000003</v>
+        <v>3.2340000000000004</v>
       </c>
       <c r="I81">
-        <v>1.3230000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="J81">
-        <v>1.1760000000000002</v>
+        <v>1.9949999999999999</v>
       </c>
       <c r="K81">
-        <v>1.0710000000000002</v>
+        <v>1.554</v>
       </c>
       <c r="L81">
-        <v>1.05</v>
+        <v>1.4489999999999998</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -3637,32 +3614,32 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82">
-        <v>3.2340000000000004</v>
+        <v>3.528</v>
       </c>
       <c r="I82">
-        <v>2.1</v>
+        <v>2.0579999999999998</v>
       </c>
       <c r="J82">
-        <v>1.9949999999999999</v>
+        <v>1.8480000000000001</v>
       </c>
       <c r="K82">
-        <v>1.554</v>
+        <v>1.4489999999999998</v>
       </c>
       <c r="L82">
-        <v>1.4489999999999998</v>
+        <v>1.4070000000000003</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -3670,69 +3647,36 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83">
-        <v>3.528</v>
+        <v>3.8640000000000003</v>
       </c>
       <c r="I83">
-        <v>2.0579999999999998</v>
+        <v>3.2760000000000002</v>
       </c>
       <c r="J83">
-        <v>1.8480000000000001</v>
+        <v>3.129</v>
       </c>
       <c r="K83">
-        <v>1.4489999999999998</v>
+        <v>2.5619999999999998</v>
       </c>
       <c r="L83">
-        <v>1.4070000000000003</v>
+        <v>2.52</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>59</v>
-      </c>
-      <c r="B84" t="s">
-        <v>65</v>
-      </c>
-      <c r="C84" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84">
-        <v>3.8640000000000003</v>
-      </c>
-      <c r="I84">
-        <v>3.2760000000000002</v>
-      </c>
-      <c r="J84">
-        <v>3.129</v>
-      </c>
-      <c r="K84">
-        <v>2.5619999999999998</v>
-      </c>
-      <c r="L84">
-        <v>2.52</v>
-      </c>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3"/>
-      <c r="O84" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FBC7AD-1A0E-4BB4-BA85-58057DA688DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF23106D-5F02-4E53-8827-A5DC7E85AE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="89">
   <si>
     <t>Catégorie</t>
   </si>
@@ -271,6 +271,42 @@
   </si>
   <si>
     <t>Cartes de visite</t>
+  </si>
+  <si>
+    <t>1 à 4</t>
+  </si>
+  <si>
+    <t>5 à 9</t>
+  </si>
+  <si>
+    <t>10 à 24</t>
+  </si>
+  <si>
+    <t>25 à 49</t>
+  </si>
+  <si>
+    <t>50 à 99</t>
+  </si>
+  <si>
+    <t>100 à 249</t>
+  </si>
+  <si>
+    <t>250 à 499</t>
+  </si>
+  <si>
+    <t>500 à 999</t>
+  </si>
+  <si>
+    <t>1000 à 2499</t>
+  </si>
+  <si>
+    <t>2500 à 4999</t>
+  </si>
+  <si>
+    <t>5000 à 9999</t>
+  </si>
+  <si>
+    <t>10000 et plus</t>
   </si>
 </sst>
 </file>
@@ -750,7 +786,7 @@
     <col min="11" max="11" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,41 +796,41 @@
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1">
-        <v>50</v>
-      </c>
-      <c r="I1" s="1">
-        <v>100</v>
-      </c>
-      <c r="J1" s="1">
-        <v>250</v>
-      </c>
-      <c r="K1" s="1">
-        <v>500</v>
-      </c>
-      <c r="L1" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M1" s="1">
-        <v>2500</v>
-      </c>
-      <c r="N1" s="1">
-        <v>5000</v>
-      </c>
-      <c r="O1" s="5">
-        <v>10000</v>
+      <c r="D1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF23106D-5F02-4E53-8827-A5DC7E85AE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60C8652-157D-46B0-A89E-23399369FB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -1044,9 +1044,15 @@
       <c r="D8">
         <v>64.8</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="E8">
+        <v>64.8</v>
+      </c>
+      <c r="F8">
+        <v>64.8</v>
+      </c>
+      <c r="G8">
+        <v>64.8</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -1069,9 +1075,15 @@
       <c r="D9">
         <v>93.6</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="E9">
+        <v>93.6</v>
+      </c>
+      <c r="F9">
+        <v>93.6</v>
+      </c>
+      <c r="G9">
+        <v>93.6</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -1094,9 +1106,15 @@
       <c r="D10">
         <v>96</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="E10">
+        <v>96</v>
+      </c>
+      <c r="F10">
+        <v>96</v>
+      </c>
+      <c r="G10">
+        <v>96</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -1119,9 +1137,15 @@
       <c r="D11">
         <v>141.6</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="E11">
+        <v>141.6</v>
+      </c>
+      <c r="F11">
+        <v>141.6</v>
+      </c>
+      <c r="G11">
+        <v>141.6</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
@@ -3264,9 +3288,15 @@
       <c r="D69">
         <v>75.375</v>
       </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
+      <c r="E69">
+        <v>75.375</v>
+      </c>
+      <c r="F69">
+        <v>75.375</v>
+      </c>
+      <c r="G69">
+        <v>75.375</v>
+      </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
@@ -3289,9 +3319,15 @@
       <c r="D70">
         <v>87.5</v>
       </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
+      <c r="E70">
+        <v>87.5</v>
+      </c>
+      <c r="F70">
+        <v>87.5</v>
+      </c>
+      <c r="G70">
+        <v>87.5</v>
+      </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
@@ -3314,9 +3350,15 @@
       <c r="D71">
         <v>124.25</v>
       </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="E71">
+        <v>124.25</v>
+      </c>
+      <c r="F71">
+        <v>124.25</v>
+      </c>
+      <c r="G71">
+        <v>124.25</v>
+      </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
@@ -3339,9 +3381,15 @@
       <c r="D72">
         <v>150.5</v>
       </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
+      <c r="E72">
+        <v>150.5</v>
+      </c>
+      <c r="F72">
+        <v>150.5</v>
+      </c>
+      <c r="G72">
+        <v>150.5</v>
+      </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
@@ -3364,9 +3412,15 @@
       <c r="D73">
         <v>176.75</v>
       </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="E73">
+        <v>176.75</v>
+      </c>
+      <c r="F73">
+        <v>176.75</v>
+      </c>
+      <c r="G73">
+        <v>176.75</v>
+      </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>

--- a/catalogue_print.xlsx
+++ b/catalogue_print.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setup\OneDrive\OneDrive - IRIS - AB Com\Bureau\reprise\site et appli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60C8652-157D-46B0-A89E-23399369FB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76986191-8B94-417A-BA1A-33CE1690736E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C577F604-72B8-4610-84EF-7A3E6DBC7BFB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="108">
   <si>
     <t>Catégorie</t>
   </si>
@@ -307,6 +307,63 @@
   </si>
   <si>
     <t>10000 et plus</t>
+  </si>
+  <si>
+    <t>Affiches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4 </t>
+  </si>
+  <si>
+    <t>90g /m2</t>
+  </si>
+  <si>
+    <t>120 ou 135g/m2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>160g/m2</t>
+  </si>
+  <si>
+    <t>250g</t>
+  </si>
+  <si>
+    <t>Cartes de correspondance</t>
+  </si>
+  <si>
+    <t>Lettre à en-tête</t>
+  </si>
+  <si>
+    <t>A4 90g</t>
+  </si>
+  <si>
+    <t>Envellope</t>
+  </si>
+  <si>
+    <t>90g</t>
+  </si>
+  <si>
+    <t>Carte restaurant</t>
+  </si>
+  <si>
+    <t>A6 fermé / A5 ouvert (1 pli)</t>
+  </si>
+  <si>
+    <t>A5 fermé /A4 ouvert (1 pli) ou 21x10 cm fermé A4 ouvert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A4 fermé / A3 ouvert (1 pli) ou 14x30 cm fermé A3 ouvert (2 plis) </t>
   </si>
 </sst>
 </file>
@@ -774,12 +831,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{520A29C8-9A76-4166-9594-E46298E59E8A}">
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="148.85546875" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" customWidth="1"/>
-    <col min="3" max="3" width="71.28515625" customWidth="1"/>
+    <col min="2" max="2" width="58.5703125" customWidth="1"/>
+    <col min="3" max="3" width="75.5703125" customWidth="1"/>
     <col min="4" max="8" width="24.140625" customWidth="1"/>
     <col min="9" max="9" width="18.85546875" customWidth="1"/>
     <col min="10" max="10" width="17.42578125" customWidth="1"/>
@@ -2452,46 +2509,18 @@
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" t="s">
-        <v>59</v>
-      </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47">
-        <v>4.7520000000000007</v>
-      </c>
-      <c r="H47">
-        <v>2.9304000000000001</v>
-      </c>
-      <c r="I47">
-        <v>1.8414000000000001</v>
-      </c>
-      <c r="J47">
-        <v>1.2117599999999999</v>
-      </c>
-      <c r="K47">
-        <v>1.0573200000000003</v>
-      </c>
-      <c r="L47">
-        <v>0.98850400000000005</v>
-      </c>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>19</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
         <v>59</v>
@@ -2500,22 +2529,22 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48">
-        <v>5.8608000000000002</v>
+        <v>4.7520000000000007</v>
       </c>
       <c r="H48">
-        <v>3.6431999999999998</v>
+        <v>2.9304000000000001</v>
       </c>
       <c r="I48">
-        <v>2.5542000000000002</v>
+        <v>1.8414000000000001</v>
       </c>
       <c r="J48">
-        <v>2.0829599999999999</v>
+        <v>1.2117599999999999</v>
       </c>
       <c r="K48">
-        <v>1.9479680000000004</v>
+        <v>1.0573200000000003</v>
       </c>
       <c r="L48">
-        <v>1.7929560000000002</v>
+        <v>0.98850400000000005</v>
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
@@ -2526,7 +2555,7 @@
         <v>19</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C49" t="s">
         <v>59</v>
@@ -2535,22 +2564,22 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49">
-        <v>7.3656000000000006</v>
+        <v>5.8608000000000002</v>
       </c>
       <c r="H49">
-        <v>5.1084000000000005</v>
+        <v>3.6431999999999998</v>
       </c>
       <c r="I49">
-        <v>4.3163999999999998</v>
+        <v>2.5542000000000002</v>
       </c>
       <c r="J49">
-        <v>3.8712960000000001</v>
+        <v>2.0829599999999999</v>
       </c>
       <c r="K49">
-        <v>3.5610960000000005</v>
+        <v>1.9479680000000004</v>
       </c>
       <c r="L49">
-        <v>3.4969880000000004</v>
+        <v>1.7929560000000002</v>
       </c>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
@@ -2558,53 +2587,45 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50">
-        <v>4.136000000000001</v>
-      </c>
+      <c r="F50" s="3"/>
       <c r="G50">
-        <v>2.31616</v>
+        <v>7.3656000000000006</v>
       </c>
       <c r="H50">
-        <v>1.5303200000000001</v>
+        <v>5.1084000000000005</v>
       </c>
       <c r="I50">
-        <v>1.1167200000000002</v>
+        <v>4.3163999999999998</v>
       </c>
       <c r="J50">
-        <v>0.50459200000000015</v>
+        <v>3.8712960000000001</v>
       </c>
       <c r="K50">
-        <v>0.28952000000000006</v>
+        <v>3.5610960000000005</v>
       </c>
       <c r="L50">
-        <v>0.18405200000000002</v>
-      </c>
-      <c r="M50">
-        <v>0.13752200000000003</v>
-      </c>
-      <c r="N50">
-        <v>0.112706</v>
-      </c>
-      <c r="O50">
-        <v>0.10009120000000001</v>
-      </c>
+        <v>3.4969880000000004</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
@@ -2612,13 +2633,13 @@
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51">
-        <v>4.3427999999999995</v>
+        <v>4.136000000000001</v>
       </c>
       <c r="G51">
-        <v>2.3988800000000001</v>
+        <v>2.31616</v>
       </c>
       <c r="H51">
-        <v>1.61304</v>
+        <v>1.5303200000000001</v>
       </c>
       <c r="I51">
         <v>1.1167200000000002</v>
@@ -2627,19 +2648,19 @@
         <v>0.50459200000000015</v>
       </c>
       <c r="K51">
-        <v>0.29365600000000003</v>
+        <v>0.28952000000000006</v>
       </c>
       <c r="L51">
-        <v>0.18612000000000001</v>
+        <v>0.18405200000000002</v>
       </c>
       <c r="M51">
         <v>0.13752200000000003</v>
       </c>
       <c r="N51">
-        <v>0.11891</v>
+        <v>0.112706</v>
       </c>
       <c r="O51">
-        <v>0.11063800000000001</v>
+        <v>0.10009120000000001</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -2647,7 +2668,7 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
         <v>8</v>
@@ -2655,118 +2676,118 @@
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52">
-        <v>4.5495999999999999</v>
+        <v>4.3427999999999995</v>
       </c>
       <c r="G52">
-        <v>2.8952000000000004</v>
+        <v>2.3988800000000001</v>
       </c>
       <c r="H52">
-        <v>1.9439200000000003</v>
+        <v>1.61304</v>
       </c>
       <c r="I52">
-        <v>1.32352</v>
+        <v>1.1167200000000002</v>
       </c>
       <c r="J52">
-        <v>0.58731200000000006</v>
+        <v>0.50459200000000015</v>
       </c>
       <c r="K52">
-        <v>0.34742399999999996</v>
+        <v>0.29365600000000003</v>
       </c>
       <c r="L52">
-        <v>0.22334400000000001</v>
+        <v>0.18612000000000001</v>
       </c>
       <c r="M52">
-        <v>0.172678</v>
+        <v>0.13752200000000003</v>
       </c>
       <c r="N52">
-        <v>0.13958999999999999</v>
+        <v>0.11891</v>
       </c>
       <c r="O52">
-        <v>0.12242560000000001</v>
+        <v>0.11063800000000001</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
-      <c r="D53">
-        <v>31.680000000000003</v>
-      </c>
-      <c r="E53">
-        <v>6.3360000000000003</v>
-      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
       <c r="F53">
-        <v>3.1680000000000001</v>
+        <v>4.5495999999999999</v>
       </c>
       <c r="G53">
-        <v>1.2672000000000001</v>
+        <v>2.8952000000000004</v>
       </c>
       <c r="H53">
-        <v>0.63360000000000005</v>
+        <v>1.9439200000000003</v>
       </c>
       <c r="I53">
-        <v>0.3696000000000001</v>
+        <v>1.32352</v>
       </c>
       <c r="J53">
-        <v>0.21824000000000005</v>
+        <v>0.58731200000000006</v>
       </c>
       <c r="K53">
-        <v>0.14080000000000001</v>
+        <v>0.34742399999999996</v>
       </c>
       <c r="L53">
-        <v>0.12903000000000001</v>
+        <v>0.22334400000000001</v>
       </c>
       <c r="M53">
-        <v>0.11444400000000003</v>
-      </c>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
+        <v>0.172678</v>
+      </c>
+      <c r="N53">
+        <v>0.13958999999999999</v>
+      </c>
+      <c r="O53">
+        <v>0.12242560000000001</v>
+      </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54">
-        <v>61.600000000000009</v>
+        <v>31.680000000000003</v>
       </c>
       <c r="E54">
-        <v>12.320000000000002</v>
+        <v>6.3360000000000003</v>
       </c>
       <c r="F54">
-        <v>6.160000000000001</v>
+        <v>3.1680000000000001</v>
       </c>
       <c r="G54">
-        <v>2.4640000000000004</v>
+        <v>1.2672000000000001</v>
       </c>
       <c r="H54">
-        <v>1.2320000000000002</v>
+        <v>0.63360000000000005</v>
       </c>
       <c r="I54">
-        <v>0.82720000000000016</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="J54">
-        <v>0.74800000000000011</v>
+        <v>0.21824000000000005</v>
       </c>
       <c r="K54">
-        <v>0.68067999999999995</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="L54">
-        <v>0.68112000000000017</v>
+        <v>0.12903000000000001</v>
       </c>
       <c r="M54">
-        <v>0.65736000000000006</v>
+        <v>0.11444400000000003</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3"/>
@@ -2776,80 +2797,80 @@
         <v>26</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>8</v>
       </c>
       <c r="D55">
-        <v>46.2</v>
+        <v>61.600000000000009</v>
       </c>
       <c r="E55">
-        <v>12.760000000000002</v>
+        <v>12.320000000000002</v>
       </c>
       <c r="F55">
-        <v>8.3600000000000012</v>
+        <v>6.160000000000001</v>
       </c>
       <c r="G55">
-        <v>4.048</v>
+        <v>2.4640000000000004</v>
       </c>
       <c r="H55">
-        <v>2.7280000000000002</v>
+        <v>1.2320000000000002</v>
       </c>
       <c r="I55">
-        <v>2.3540000000000001</v>
+        <v>0.82720000000000016</v>
       </c>
       <c r="J55">
-        <v>1.9360000000000002</v>
+        <v>0.74800000000000011</v>
       </c>
       <c r="K55">
-        <v>1.6280000000000003</v>
-      </c>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
+        <v>0.68067999999999995</v>
+      </c>
+      <c r="L55">
+        <v>0.68112000000000017</v>
+      </c>
+      <c r="M55">
+        <v>0.65736000000000006</v>
+      </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
         <v>8</v>
       </c>
       <c r="D56">
-        <v>31.680000000000003</v>
+        <v>46.2</v>
       </c>
       <c r="E56">
-        <v>6.3360000000000003</v>
+        <v>12.760000000000002</v>
       </c>
       <c r="F56">
-        <v>3.1680000000000001</v>
+        <v>8.3600000000000012</v>
       </c>
       <c r="G56">
-        <v>1.2672000000000001</v>
+        <v>4.048</v>
       </c>
       <c r="H56">
-        <v>0.63360000000000005</v>
+        <v>2.7280000000000002</v>
       </c>
       <c r="I56">
-        <v>0.3696000000000001</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="J56">
-        <v>0.21824000000000005</v>
+        <v>1.9360000000000002</v>
       </c>
       <c r="K56">
-        <v>0.14080000000000001</v>
-      </c>
-      <c r="L56">
-        <v>0.12903000000000001</v>
-      </c>
-      <c r="M56">
-        <v>0.11444400000000003</v>
-      </c>
+        <v>1.6280000000000003</v>
+      </c>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
     </row>
@@ -2858,39 +2879,41 @@
         <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
         <v>8</v>
       </c>
       <c r="D57">
-        <v>70.400000000000006</v>
+        <v>31.680000000000003</v>
       </c>
       <c r="E57">
-        <v>14.080000000000002</v>
+        <v>6.3360000000000003</v>
       </c>
       <c r="F57">
-        <v>7.0400000000000009</v>
+        <v>3.1680000000000001</v>
       </c>
       <c r="G57">
-        <v>2.8160000000000003</v>
+        <v>1.2672000000000001</v>
       </c>
       <c r="H57">
-        <v>1.4080000000000001</v>
+        <v>0.63360000000000005</v>
       </c>
       <c r="I57">
-        <v>0.99109999999999998</v>
+        <v>0.3696000000000001</v>
       </c>
       <c r="J57">
-        <v>0.51612000000000002</v>
+        <v>0.21824000000000005</v>
       </c>
       <c r="K57">
-        <v>0.46002000000000004</v>
+        <v>0.14080000000000001</v>
       </c>
       <c r="L57">
-        <v>0.43571000000000004</v>
-      </c>
-      <c r="M57" s="3"/>
+        <v>0.12903000000000001</v>
+      </c>
+      <c r="M57">
+        <v>0.11444400000000003</v>
+      </c>
       <c r="N57" s="3"/>
       <c r="O57" s="3"/>
     </row>
@@ -2899,67 +2922,77 @@
         <v>30</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
         <v>8</v>
       </c>
       <c r="D58">
-        <v>129.03</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="E58">
-        <v>12.760000000000002</v>
+        <v>14.080000000000002</v>
       </c>
       <c r="F58">
-        <v>8.3600000000000012</v>
+        <v>7.0400000000000009</v>
       </c>
       <c r="G58">
-        <v>4.048</v>
+        <v>2.8160000000000003</v>
       </c>
       <c r="H58">
-        <v>2.7280000000000002</v>
+        <v>1.4080000000000001</v>
       </c>
       <c r="I58">
-        <v>2.3540000000000001</v>
+        <v>0.99109999999999998</v>
       </c>
       <c r="J58">
-        <v>1.9360000000000002</v>
+        <v>0.51612000000000002</v>
       </c>
       <c r="K58">
-        <v>1.6280000000000003</v>
-      </c>
-      <c r="L58" s="3"/>
+        <v>0.46002000000000004</v>
+      </c>
+      <c r="L58">
+        <v>0.43571000000000004</v>
+      </c>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" s="3"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
+      <c r="D59">
+        <v>129.03</v>
+      </c>
+      <c r="E59">
+        <v>12.760000000000002</v>
+      </c>
+      <c r="F59">
+        <v>8.3600000000000012</v>
+      </c>
+      <c r="G59">
+        <v>4.048</v>
+      </c>
+      <c r="H59">
+        <v>2.7280000000000002</v>
+      </c>
       <c r="I59">
-        <v>0.19899999999999998</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="J59">
-        <v>0.1196</v>
+        <v>1.9360000000000002</v>
       </c>
       <c r="K59">
-        <v>7.9799999999999996E-2</v>
-      </c>
-      <c r="L59">
-        <v>4.5899999999999996E-2</v>
-      </c>
+        <v>1.6280000000000003</v>
+      </c>
+      <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" s="3"/>
@@ -2972,7 +3005,7 @@
         <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2980,16 +3013,16 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60">
-        <v>0.29899999999999999</v>
+        <v>0.19899999999999998</v>
       </c>
       <c r="J60">
-        <v>0.15959999999999999</v>
+        <v>0.1196</v>
       </c>
       <c r="K60">
-        <v>9.98E-2</v>
+        <v>7.9799999999999996E-2</v>
       </c>
       <c r="L60">
-        <v>5.9900000000000002E-2</v>
+        <v>4.5899999999999996E-2</v>
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
@@ -3000,10 +3033,10 @@
         <v>76</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -3011,16 +3044,16 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61">
-        <v>0.34899999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="J61">
-        <v>0.18359999999999999</v>
+        <v>0.15959999999999999</v>
       </c>
       <c r="K61">
-        <v>0.1118</v>
+        <v>9.98E-2</v>
       </c>
       <c r="L61">
-        <v>6.4899999999999999E-2</v>
+        <v>5.9900000000000002E-2</v>
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
@@ -3034,7 +3067,7 @@
         <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3042,30 +3075,30 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62">
-        <v>0.39899999999999997</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="J62">
-        <v>0.1996</v>
+        <v>0.18359999999999999</v>
       </c>
       <c r="K62">
-        <v>0.1198</v>
+        <v>0.1118</v>
       </c>
       <c r="L62">
-        <v>6.9900000000000004E-2</v>
+        <v>6.4899999999999999E-2</v>
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
       <c r="O62" s="3"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
-        <v>33</v>
+      <c r="A63" t="s">
+        <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3073,23 +3106,19 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63">
-        <v>0.4536</v>
+        <v>0.39899999999999997</v>
       </c>
       <c r="J63">
-        <v>0.29959199999999997</v>
+        <v>0.1996</v>
       </c>
       <c r="K63">
-        <v>0.247032</v>
+        <v>0.1198</v>
       </c>
       <c r="L63">
-        <v>0.1764</v>
-      </c>
-      <c r="M63">
-        <v>8.3044800000000016E-2</v>
-      </c>
-      <c r="N63">
-        <v>7.3583999999999997E-2</v>
-      </c>
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
       <c r="O63" s="3"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3097,7 +3126,7 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
         <v>34</v>
@@ -3108,22 +3137,22 @@
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64">
-        <v>0.3528</v>
+        <v>0.4536</v>
       </c>
       <c r="J64">
-        <v>0.2016</v>
+        <v>0.29959199999999997</v>
       </c>
       <c r="K64">
-        <v>0.14716799999999999</v>
+        <v>0.247032</v>
       </c>
       <c r="L64">
-        <v>0.12220200000000001</v>
+        <v>0.1764</v>
       </c>
       <c r="M64">
-        <v>5.0457600000000005E-2</v>
+        <v>8.3044800000000016E-2</v>
       </c>
       <c r="N64">
-        <v>3.9682800000000004E-2</v>
+        <v>7.3583999999999997E-2</v>
       </c>
       <c r="O64" s="3"/>
     </row>
@@ -3132,7 +3161,7 @@
         <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
         <v>34</v>
@@ -3143,22 +3172,22 @@
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65">
-        <v>0.3024</v>
+        <v>0.3528</v>
       </c>
       <c r="J65">
-        <v>0.14615999999999998</v>
+        <v>0.2016</v>
       </c>
       <c r="K65">
-        <v>9.8280000000000006E-2</v>
+        <v>0.14716799999999999</v>
       </c>
       <c r="L65">
-        <v>7.7525999999999998E-2</v>
+        <v>0.12220200000000001</v>
       </c>
       <c r="M65">
-        <v>3.4164000000000007E-2</v>
+        <v>5.0457600000000005E-2</v>
       </c>
       <c r="N65">
-        <v>2.7068400000000003E-2</v>
+        <v>3.9682800000000004E-2</v>
       </c>
       <c r="O65" s="3"/>
     </row>
@@ -3167,10 +3196,10 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C66" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -3178,28 +3207,22 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66">
-        <f>(37*(0.85*2))/100</f>
-        <v>0.629</v>
+        <v>0.3024</v>
       </c>
       <c r="J66">
-        <f>(74*(0.85*2))/250</f>
-        <v>0.50319999999999998</v>
+        <v>0.14615999999999998</v>
       </c>
       <c r="K66">
-        <f>(99*(0.85*2))/500</f>
-        <v>0.33659999999999995</v>
+        <v>9.8280000000000006E-2</v>
       </c>
       <c r="L66">
-        <f>(139*(0.85*2))/1000</f>
-        <v>0.23629999999999998</v>
+        <v>7.7525999999999998E-2</v>
       </c>
       <c r="M66">
-        <f>(265*(0.85*2))/2500</f>
-        <v>0.1802</v>
+        <v>3.4164000000000007E-2</v>
       </c>
       <c r="N66">
-        <f>(481*(0.85*2))/5000</f>
-        <v>0.16353999999999999</v>
+        <v>2.7068400000000003E-2</v>
       </c>
       <c r="O66" s="3"/>
     </row>
@@ -3208,7 +3231,7 @@
         <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
         <v>38</v>
@@ -3219,28 +3242,28 @@
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67">
-        <f>(27*(0.85*2))/100</f>
-        <v>0.45899999999999996</v>
+        <f>(37*(0.85*2))/100</f>
+        <v>0.629</v>
       </c>
       <c r="J67">
-        <f>(40*(0.85*2))/250</f>
-        <v>0.27200000000000002</v>
+        <f>(74*(0.85*2))/250</f>
+        <v>0.50319999999999998</v>
       </c>
       <c r="K67">
-        <f>(48*(0.85*2))/500</f>
-        <v>0.16319999999999998</v>
+        <f>(99*(0.85*2))/500</f>
+        <v>0.33659999999999995</v>
       </c>
       <c r="L67">
-        <f>(66*(0.85*2))/1000</f>
-        <v>0.11220000000000001</v>
+        <f>(139*(0.85*2))/1000</f>
+        <v>0.23629999999999998</v>
       </c>
       <c r="M67">
-        <f>(122*(0.85*2))/2500</f>
-        <v>8.2960000000000006E-2</v>
+        <f>(265*(0.85*2))/2500</f>
+        <v>0.1802</v>
       </c>
       <c r="N67">
-        <f>(213*(0.85*2))/5000</f>
-        <v>7.2419999999999998E-2</v>
+        <f>(481*(0.85*2))/5000</f>
+        <v>0.16353999999999999</v>
       </c>
       <c r="O67" s="3"/>
     </row>
@@ -3248,59 +3271,69 @@
       <c r="A68" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>39</v>
+      <c r="B68" t="s">
+        <v>36</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68">
-        <v>2.16</v>
-      </c>
+      <c r="H68" s="3"/>
       <c r="I68">
-        <v>1.72</v>
+        <f>(27*(0.85*2))/100</f>
+        <v>0.45899999999999996</v>
       </c>
       <c r="J68">
-        <v>1.51</v>
+        <f>(40*(0.85*2))/250</f>
+        <v>0.27200000000000002</v>
       </c>
       <c r="K68">
-        <v>1.26</v>
-      </c>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
+        <f>(48*(0.85*2))/500</f>
+        <v>0.16319999999999998</v>
+      </c>
+      <c r="L68">
+        <f>(66*(0.85*2))/1000</f>
+        <v>0.11220000000000001</v>
+      </c>
+      <c r="M68">
+        <f>(122*(0.85*2))/2500</f>
+        <v>8.2960000000000006E-2</v>
+      </c>
+      <c r="N68">
+        <f>(213*(0.85*2))/5000</f>
+        <v>7.2419999999999998E-2</v>
+      </c>
       <c r="O68" s="3"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" t="s">
-        <v>40</v>
+      <c r="A69" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="C69" t="s">
         <v>8</v>
       </c>
-      <c r="D69">
-        <v>75.375</v>
-      </c>
-      <c r="E69">
-        <v>75.375</v>
-      </c>
-      <c r="F69">
-        <v>75.375</v>
-      </c>
-      <c r="G69">
-        <v>75.375</v>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69">
+        <v>2.16</v>
+      </c>
+      <c r="I69">
+        <v>1.72</v>
+      </c>
+      <c r="J69">
+        <v>1.51</v>
+      </c>
+      <c r="K69">
+        <v>1.26</v>
+      </c>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
@@ -3311,22 +3344,22 @@
         <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C70" t="s">
         <v>8</v>
       </c>
       <c r="D70">
-        <v>87.5</v>
+        <v>75.375</v>
       </c>
       <c r="E70">
-        <v>87.5</v>
+        <v>75.375</v>
       </c>
       <c r="F70">
-        <v>87.5</v>
+        <v>75.375</v>
       </c>
       <c r="G70">
-        <v>87.5</v>
+        <v>75.375</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -3342,22 +3375,22 @@
         <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
       </c>
       <c r="D71">
-        <v>124.25</v>
+        <v>87.5</v>
       </c>
       <c r="E71">
-        <v>124.25</v>
+        <v>87.5</v>
       </c>
       <c r="F71">
-        <v>124.25</v>
+        <v>87.5</v>
       </c>
       <c r="G71">
-        <v>124.25</v>
+        <v>87.5</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -3373,22 +3406,22 @@
         <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C72" t="s">
         <v>8</v>
       </c>
       <c r="D72">
-        <v>150.5</v>
+        <v>124.25</v>
       </c>
       <c r="E72">
-        <v>150.5</v>
+        <v>124.25</v>
       </c>
       <c r="F72">
-        <v>150.5</v>
+        <v>124.25</v>
       </c>
       <c r="G72">
-        <v>150.5</v>
+        <v>124.25</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -3404,22 +3437,22 @@
         <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
         <v>8</v>
       </c>
       <c r="D73">
-        <v>176.75</v>
+        <v>150.5</v>
       </c>
       <c r="E73">
-        <v>176.75</v>
+        <v>150.5</v>
       </c>
       <c r="F73">
-        <v>176.75</v>
+        <v>150.5</v>
       </c>
       <c r="G73">
-        <v>176.75</v>
+        <v>150.5</v>
       </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -3432,37 +3465,33 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
         <v>8</v>
       </c>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
+      <c r="D74">
+        <v>176.75</v>
+      </c>
+      <c r="E74">
+        <v>176.75</v>
+      </c>
+      <c r="F74">
+        <v>176.75</v>
+      </c>
+      <c r="G74">
+        <v>176.75</v>
+      </c>
       <c r="H74" s="3"/>
-      <c r="I74">
-        <v>0.96800000000000008</v>
-      </c>
-      <c r="J74">
-        <v>0.74800000000000011</v>
-      </c>
-      <c r="K74">
-        <v>0.62480000000000002</v>
-      </c>
-      <c r="L74">
-        <v>0.5918000000000001</v>
-      </c>
-      <c r="M74">
-        <v>0.45408000000000004</v>
-      </c>
-      <c r="N74">
-        <v>0.35376000000000002</v>
-      </c>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+      <c r="K74" s="3"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
       <c r="O74" s="3"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
@@ -3470,10 +3499,10 @@
         <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -3481,22 +3510,22 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75">
-        <v>1.254</v>
+        <v>0.96800000000000008</v>
       </c>
       <c r="J75">
-        <v>1.1176000000000001</v>
+        <v>0.74800000000000011</v>
       </c>
       <c r="K75">
-        <v>0.9284</v>
+        <v>0.62480000000000002</v>
       </c>
       <c r="L75">
-        <v>0.78980000000000006</v>
+        <v>0.5918000000000001</v>
       </c>
       <c r="M75">
-        <v>0.54032000000000002</v>
+        <v>0.45408000000000004</v>
       </c>
       <c r="N75">
-        <v>0.41095999999999999</v>
+        <v>0.35376000000000002</v>
       </c>
       <c r="O75" s="3"/>
     </row>
@@ -3505,10 +3534,10 @@
         <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -3516,22 +3545,22 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76">
-        <v>1.034</v>
+        <v>1.254</v>
       </c>
       <c r="J76">
-        <v>0.79200000000000004</v>
+        <v>1.1176000000000001</v>
       </c>
       <c r="K76">
-        <v>0.66</v>
+        <v>0.9284</v>
       </c>
       <c r="L76">
-        <v>0.62260000000000004</v>
+        <v>0.78980000000000006</v>
       </c>
       <c r="M76">
-        <v>0.52888000000000002</v>
+        <v>0.54032000000000002</v>
       </c>
       <c r="N76">
-        <v>0.38324000000000003</v>
+        <v>0.41095999999999999</v>
       </c>
       <c r="O76" s="3"/>
     </row>
@@ -3540,10 +3569,10 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -3551,56 +3580,58 @@
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
       <c r="I77">
-        <v>1.3420000000000001</v>
+        <v>1.034</v>
       </c>
       <c r="J77">
-        <v>1.1792000000000002</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="K77">
-        <v>0.98120000000000007</v>
+        <v>0.66</v>
       </c>
       <c r="L77">
-        <v>0.83600000000000008</v>
+        <v>0.62260000000000004</v>
       </c>
       <c r="M77">
-        <v>0.5684800000000001</v>
+        <v>0.52888000000000002</v>
       </c>
       <c r="N77">
-        <v>0.44703999999999999</v>
+        <v>0.38324000000000003</v>
       </c>
       <c r="O77" s="3"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78">
-        <v>1.1760000000000002</v>
-      </c>
+      <c r="H78" s="3"/>
       <c r="I78">
-        <v>0.73499999999999999</v>
+        <v>1.3420000000000001</v>
       </c>
       <c r="J78">
-        <v>0.60899999999999999</v>
+        <v>1.1792000000000002</v>
       </c>
       <c r="K78">
-        <v>0.56700000000000006</v>
+        <v>0.98120000000000007</v>
       </c>
       <c r="L78">
-        <v>0.56700000000000006</v>
-      </c>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
+        <v>0.83600000000000008</v>
+      </c>
+      <c r="M78">
+        <v>0.5684800000000001</v>
+      </c>
+      <c r="N78">
+        <v>0.44703999999999999</v>
+      </c>
       <c r="O78" s="3"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
@@ -3608,7 +3639,7 @@
         <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
@@ -3618,19 +3649,19 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79">
-        <v>1.6380000000000001</v>
+        <v>1.1760000000000002</v>
       </c>
       <c r="I79">
-        <v>1.1130000000000002</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="J79">
-        <v>1.0710000000000002</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="K79">
-        <v>0.98699999999999999</v>
+        <v>0.56700000000000006</v>
       </c>
       <c r="L79">
-        <v>0.92400000000000004</v>
+        <v>0.56700000000000006</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -3641,7 +3672,7 @@
         <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C80" t="s">
         <v>8</v>
@@ -3651,19 +3682,19 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80">
-        <v>2.3520000000000003</v>
+        <v>1.6380000000000001</v>
       </c>
       <c r="I80">
-        <v>1.3230000000000002</v>
+        <v>1.1130000000000002</v>
       </c>
       <c r="J80">
-        <v>1.1760000000000002</v>
+        <v>1.0710000000000002</v>
       </c>
       <c r="K80">
-        <v>1.0710000000000002</v>
+        <v>0.98699999999999999</v>
       </c>
       <c r="L80">
-        <v>1.05</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -3674,7 +3705,7 @@
         <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C81" t="s">
         <v>8</v>
@@ -3684,19 +3715,19 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81">
-        <v>3.2340000000000004</v>
+        <v>2.3520000000000003</v>
       </c>
       <c r="I81">
-        <v>2.1</v>
+        <v>1.3230000000000002</v>
       </c>
       <c r="J81">
-        <v>1.9949999999999999</v>
+        <v>1.1760000000000002</v>
       </c>
       <c r="K81">
-        <v>1.554</v>
+        <v>1.0710000000000002</v>
       </c>
       <c r="L81">
-        <v>1.4489999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -3707,7 +3738,7 @@
         <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
         <v>8</v>
@@ -3717,19 +3748,19 @@
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82">
-        <v>3.528</v>
+        <v>3.2340000000000004</v>
       </c>
       <c r="I82">
-        <v>2.0579999999999998</v>
+        <v>2.1</v>
       </c>
       <c r="J82">
-        <v>1.8480000000000001</v>
+        <v>1.9949999999999999</v>
       </c>
       <c r="K82">
+        <v>1.554</v>
+      </c>
+      <c r="L82">
         <v>1.4489999999999998</v>
-      </c>
-      <c r="L82">
-        <v>1.4070000000000003</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
@@ -3740,7 +3771,7 @@
         <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -3750,24 +3781,499 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83">
-        <v>3.8640000000000003</v>
+        <v>3.528</v>
       </c>
       <c r="I83">
-        <v>3.2760000000000002</v>
+        <v>2.0579999999999998</v>
       </c>
       <c r="J83">
-        <v>3.129</v>
+        <v>1.8480000000000001</v>
       </c>
       <c r="K83">
-        <v>2.5619999999999998</v>
+        <v>1.4489999999999998</v>
       </c>
       <c r="L83">
-        <v>2.52</v>
+        <v>1.4070000000000003</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" s="3"/>
     </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>51</v>
+      </c>
+      <c r="B84" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84">
+        <v>3.8640000000000003</v>
+      </c>
+      <c r="I84">
+        <v>3.2760000000000002</v>
+      </c>
+      <c r="J84">
+        <v>3.129</v>
+      </c>
+      <c r="K84">
+        <v>2.5619999999999998</v>
+      </c>
+      <c r="L84">
+        <v>2.52</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85">
+        <v>3.3</v>
+      </c>
+      <c r="G85">
+        <v>1.56</v>
+      </c>
+      <c r="H85">
+        <v>0.82</v>
+      </c>
+      <c r="I85">
+        <v>0.46</v>
+      </c>
+      <c r="J85">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="K85" s="3"/>
+      <c r="L85" s="3"/>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86" t="s">
+        <v>35</v>
+      </c>
+      <c r="C86" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86">
+        <v>3.08</v>
+      </c>
+      <c r="G86">
+        <v>1.6</v>
+      </c>
+      <c r="H86">
+        <v>0.84</v>
+      </c>
+      <c r="I86">
+        <v>0.48</v>
+      </c>
+      <c r="J86">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="K86" s="3"/>
+      <c r="L86" s="3"/>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" t="s">
+        <v>93</v>
+      </c>
+      <c r="C87" t="s">
+        <v>91</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87">
+        <v>3.8</v>
+      </c>
+      <c r="G87">
+        <v>1.96</v>
+      </c>
+      <c r="H87">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="I87">
+        <v>0.7</v>
+      </c>
+      <c r="J87">
+        <v>0.36799999999999999</v>
+      </c>
+      <c r="K87" s="3"/>
+      <c r="L87" s="3"/>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B88" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88">
+        <v>3.6</v>
+      </c>
+      <c r="G88">
+        <v>1.68</v>
+      </c>
+      <c r="H88">
+        <v>0.92</v>
+      </c>
+      <c r="I88">
+        <v>0.6</v>
+      </c>
+      <c r="J88">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="K88" s="3"/>
+      <c r="L88" s="3"/>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89">
+        <v>13.2</v>
+      </c>
+      <c r="F89">
+        <v>8</v>
+      </c>
+      <c r="G89">
+        <v>4.24</v>
+      </c>
+      <c r="H89">
+        <v>2.42</v>
+      </c>
+      <c r="I89">
+        <v>1.38</v>
+      </c>
+      <c r="J89">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90">
+        <v>7.2</v>
+      </c>
+      <c r="F90">
+        <v>4.2</v>
+      </c>
+      <c r="G90">
+        <v>2.12</v>
+      </c>
+      <c r="H90">
+        <v>1.64</v>
+      </c>
+      <c r="I90">
+        <v>1.04</v>
+      </c>
+      <c r="J90">
+        <v>0.64</v>
+      </c>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+      <c r="B91" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" t="s">
+        <v>92</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91">
+        <v>11.8</v>
+      </c>
+      <c r="F91">
+        <v>7.9</v>
+      </c>
+      <c r="G91">
+        <v>5.6</v>
+      </c>
+      <c r="H91">
+        <v>3.78</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>89</v>
+      </c>
+      <c r="B92" t="s">
+        <v>94</v>
+      </c>
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F92">
+        <v>17.8</v>
+      </c>
+      <c r="G92">
+        <v>8</v>
+      </c>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="3"/>
+      <c r="L92" s="3"/>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93">
+        <v>0.45</v>
+      </c>
+      <c r="J93">
+        <v>0.24</v>
+      </c>
+      <c r="K93">
+        <v>0.16</v>
+      </c>
+      <c r="L93">
+        <v>0.12</v>
+      </c>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3"/>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94">
+        <v>0.18</v>
+      </c>
+      <c r="K94">
+        <v>0.12</v>
+      </c>
+      <c r="L94">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="M94">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N94">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95" t="s">
+        <v>59</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95">
+        <v>0.26</v>
+      </c>
+      <c r="K95">
+        <v>0.15</v>
+      </c>
+      <c r="L95">
+        <v>0.115</v>
+      </c>
+      <c r="M95">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="N95">
+        <v>0.06</v>
+      </c>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>103</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96">
+        <v>0.7</v>
+      </c>
+      <c r="J96">
+        <v>0.36</v>
+      </c>
+      <c r="K96">
+        <v>0.26</v>
+      </c>
+      <c r="L96">
+        <v>0.21</v>
+      </c>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97" t="s">
+        <v>59</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3"/>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>104</v>
+      </c>
+      <c r="B99" t="s">
+        <v>107</v>
+      </c>
+      <c r="C99" t="s">
+        <v>59</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3"/>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
